--- a/AAII_Financials/Quarterly/IMAB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IMAB_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="92">
   <si>
     <t>IMAB</t>
   </si>
@@ -656,150 +656,157 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44196</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44104</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44012</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43830</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43738</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43646</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43465</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43373</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43281</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E8" s="3">
         <v>2700</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3">
         <v>7200</v>
       </c>
-      <c r="G8" s="3">
-        <v>9700</v>
-      </c>
       <c r="H8" s="3">
+        <v>9800</v>
+      </c>
+      <c r="I8" s="3">
         <v>2500</v>
       </c>
-      <c r="I8" s="3">
-        <v>213000</v>
-      </c>
       <c r="J8" s="3">
-        <v>0</v>
+        <v>214500</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
       </c>
       <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
         <v>4300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3300</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -809,14 +816,14 @@
       <c r="E9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3">
         <v>3800</v>
       </c>
-      <c r="G9" s="3">
-        <v>6400</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
+      <c r="H9" s="3">
+        <v>6500</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
@@ -854,8 +861,11 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -865,15 +875,15 @@
       <c r="E10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3">
         <v>3400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3300</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
       </c>
@@ -910,8 +920,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -932,64 +945,68 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>61600</v>
+        <v>112700</v>
       </c>
       <c r="E12" s="3">
-        <v>62500</v>
+        <v>62100</v>
       </c>
       <c r="F12" s="3">
-        <v>62500</v>
+        <v>62900</v>
       </c>
       <c r="G12" s="3">
-        <v>85600</v>
+        <v>62900</v>
       </c>
       <c r="H12" s="3">
-        <v>81900</v>
+        <v>86200</v>
       </c>
       <c r="I12" s="3">
-        <v>74900</v>
+        <v>82400</v>
       </c>
       <c r="J12" s="3">
+        <v>75400</v>
+      </c>
+      <c r="K12" s="3">
         <v>35400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>62900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>120700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>45800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>41800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>65600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>17100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>31000</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1044,8 +1061,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1073,12 +1093,12 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>3300</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1094,14 +1114,17 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1156,8 +1179,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1175,120 +1201,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>95500</v>
+      <c r="D17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E17" s="3">
-        <v>120900</v>
+        <v>96100</v>
       </c>
       <c r="F17" s="3">
-        <v>120400</v>
+        <v>121700</v>
       </c>
       <c r="G17" s="3">
-        <v>153900</v>
+        <v>121300</v>
       </c>
       <c r="H17" s="3">
-        <v>144200</v>
+        <v>155000</v>
       </c>
       <c r="I17" s="3">
-        <v>106800</v>
+        <v>145200</v>
       </c>
       <c r="J17" s="3">
+        <v>107500</v>
+      </c>
+      <c r="K17" s="3">
         <v>54600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>87200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>218000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>46900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>132500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>75800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>20500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>33800</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>-92800</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-113300</v>
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-93400</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G18" s="3">
-        <v>-144200</v>
+        <v>-114100</v>
       </c>
       <c r="H18" s="3">
-        <v>-141800</v>
+        <v>-145200</v>
       </c>
       <c r="I18" s="3">
-        <v>106200</v>
+        <v>-142700</v>
       </c>
       <c r="J18" s="3">
+        <v>106900</v>
+      </c>
+      <c r="K18" s="3">
         <v>-54600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-87200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-213700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-44700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-130100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-67500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-17100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-30600</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1309,64 +1342,68 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-13900</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-31300</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G20" s="3">
-        <v>-29100</v>
+        <v>-31500</v>
       </c>
       <c r="H20" s="3">
-        <v>-7300</v>
+        <v>-29300</v>
       </c>
       <c r="I20" s="3">
-        <v>41000</v>
+        <v>-7400</v>
       </c>
       <c r="J20" s="3">
+        <v>41300</v>
+      </c>
+      <c r="K20" s="3">
         <v>56300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>8900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>7600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>6500</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1385,58 +1422,61 @@
       <c r="H21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I21" s="3">
-        <v>149200</v>
+      <c r="I21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J21" s="3">
+        <v>150200</v>
+      </c>
+      <c r="K21" s="3">
         <v>2800</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3">
         <v>-206700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-34900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-134200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-58900</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>-23900</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
@@ -1448,93 +1488,99 @@
         <v>0</v>
       </c>
       <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1400</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-106700</v>
+        <v>-203800</v>
       </c>
       <c r="E23" s="3">
-        <v>-201600</v>
+        <v>-107400</v>
       </c>
       <c r="F23" s="3">
-        <v>-144600</v>
+        <v>-202900</v>
       </c>
       <c r="G23" s="3">
-        <v>-173300</v>
+        <v>-145500</v>
       </c>
       <c r="H23" s="3">
-        <v>-149100</v>
+        <v>-174500</v>
       </c>
       <c r="I23" s="3">
-        <v>147200</v>
+        <v>-150100</v>
       </c>
       <c r="J23" s="3">
+        <v>148200</v>
+      </c>
+      <c r="K23" s="3">
         <v>1700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-82900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-208500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-35900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-135300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-61800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-17000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-25500</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1542,23 +1588,23 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>-400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1700</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
@@ -1572,16 +1618,16 @@
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
+      <c r="R24" s="3">
+        <v>0</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
@@ -1589,8 +1635,11 @@
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1645,120 +1694,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>-106700</v>
+      <c r="D26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E26" s="3">
-        <v>-201700</v>
+        <v>-107400</v>
       </c>
       <c r="F26" s="3">
-        <v>-144600</v>
+        <v>-203000</v>
       </c>
       <c r="G26" s="3">
-        <v>-173300</v>
+        <v>-145500</v>
       </c>
       <c r="H26" s="3">
-        <v>-148600</v>
+        <v>-174500</v>
       </c>
       <c r="I26" s="3">
-        <v>145500</v>
+        <v>-149700</v>
       </c>
       <c r="J26" s="3">
+        <v>146500</v>
+      </c>
+      <c r="K26" s="3">
         <v>1700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-82900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-208500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-35900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-135300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-62000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-17200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-25500</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>-106700</v>
+      <c r="D27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E27" s="3">
-        <v>-201700</v>
+        <v>-107400</v>
       </c>
       <c r="F27" s="3">
-        <v>-144600</v>
+        <v>-203000</v>
       </c>
       <c r="G27" s="3">
-        <v>-173300</v>
+        <v>-145500</v>
       </c>
       <c r="H27" s="3">
-        <v>-148600</v>
+        <v>-174500</v>
       </c>
       <c r="I27" s="3">
-        <v>145500</v>
+        <v>-149700</v>
       </c>
       <c r="J27" s="3">
+        <v>146500</v>
+      </c>
+      <c r="K27" s="3">
         <v>1700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-82900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-213300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-35900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-135300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-62000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-17200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-25500</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1813,8 +1871,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1869,8 +1930,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1925,8 +1989,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1981,120 +2048,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>13900</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F32" s="3">
-        <v>31300</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
+        <v>14000</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G32" s="3">
-        <v>29100</v>
+        <v>31500</v>
       </c>
       <c r="H32" s="3">
-        <v>7300</v>
+        <v>29300</v>
       </c>
       <c r="I32" s="3">
-        <v>-41000</v>
+        <v>7400</v>
       </c>
       <c r="J32" s="3">
+        <v>-41300</v>
+      </c>
+      <c r="K32" s="3">
         <v>-56300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-8900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-7600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-6500</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>-106700</v>
+      <c r="D33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E33" s="3">
-        <v>-201700</v>
+        <v>-107400</v>
       </c>
       <c r="F33" s="3">
-        <v>-144600</v>
+        <v>-203000</v>
       </c>
       <c r="G33" s="3">
-        <v>-173300</v>
+        <v>-145500</v>
       </c>
       <c r="H33" s="3">
-        <v>-148600</v>
+        <v>-174500</v>
       </c>
       <c r="I33" s="3">
-        <v>145500</v>
+        <v>-149700</v>
       </c>
       <c r="J33" s="3">
+        <v>146500</v>
+      </c>
+      <c r="K33" s="3">
         <v>1700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-82900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-213300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-35900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-135300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-62000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-17200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-25500</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2149,125 +2225,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>-106700</v>
+      <c r="D35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E35" s="3">
-        <v>-201700</v>
+        <v>-107400</v>
       </c>
       <c r="F35" s="3">
-        <v>-144600</v>
+        <v>-203000</v>
       </c>
       <c r="G35" s="3">
-        <v>-173300</v>
+        <v>-145500</v>
       </c>
       <c r="H35" s="3">
-        <v>-148600</v>
+        <v>-174500</v>
       </c>
       <c r="I35" s="3">
-        <v>145500</v>
+        <v>-149700</v>
       </c>
       <c r="J35" s="3">
+        <v>146500</v>
+      </c>
+      <c r="K35" s="3">
         <v>1700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-82900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-213300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-35900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-135300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-62000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-17200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-25500</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44196</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44104</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44012</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43830</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43738</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43646</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43465</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43373</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43281</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2288,8 +2373,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2310,47 +2396,48 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>325800</v>
+        <v>297700</v>
       </c>
       <c r="E41" s="3">
-        <v>443800</v>
+        <v>328000</v>
       </c>
       <c r="F41" s="3">
-        <v>512400</v>
+        <v>446800</v>
       </c>
       <c r="G41" s="3">
-        <v>486500</v>
+        <v>515900</v>
       </c>
       <c r="H41" s="3">
-        <v>599500</v>
+        <v>489900</v>
       </c>
       <c r="I41" s="3">
-        <v>657100</v>
+        <v>603600</v>
       </c>
       <c r="J41" s="3">
+        <v>661600</v>
+      </c>
+      <c r="K41" s="3">
         <v>408700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>221800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>163400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>178800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>200200</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2366,46 +2453,49 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>80900</v>
+        <v>19900</v>
       </c>
       <c r="E42" s="3">
-        <v>32500</v>
+        <v>81500</v>
       </c>
       <c r="F42" s="3">
-        <v>29200</v>
+        <v>32700</v>
       </c>
       <c r="G42" s="3">
-        <v>104000</v>
+        <v>29400</v>
       </c>
       <c r="H42" s="3">
-        <v>58300</v>
+        <v>104700</v>
       </c>
       <c r="I42" s="3">
+        <v>58700</v>
+      </c>
+      <c r="J42" s="3">
         <v>4400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>7700</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
+      <c r="O42" s="3">
+        <v>0</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
@@ -2422,47 +2512,50 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E43" s="3">
-        <v>0</v>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F43" s="3">
-        <v>40300</v>
+        <v>0</v>
       </c>
       <c r="G43" s="3">
-        <v>39600</v>
+        <v>40500</v>
       </c>
       <c r="H43" s="3">
-        <v>33500</v>
+        <v>39900</v>
       </c>
       <c r="I43" s="3">
-        <v>49400</v>
+        <v>33800</v>
       </c>
       <c r="J43" s="3">
+        <v>49800</v>
+      </c>
+      <c r="K43" s="3">
         <v>10700</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3">
         <v>4200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>12300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>18400</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2478,26 +2571,29 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="3">
-        <v>0</v>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F44" s="3">
         <v>0</v>
       </c>
       <c r="G44" s="3">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3">
         <v>3800</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2513,8 +2609,8 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
@@ -2534,47 +2630,50 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>17900</v>
+        <v>7200</v>
       </c>
       <c r="E45" s="3">
-        <v>24400</v>
+        <v>18000</v>
       </c>
       <c r="F45" s="3">
-        <v>13900</v>
+        <v>24600</v>
       </c>
       <c r="G45" s="3">
-        <v>26300</v>
+        <v>14000</v>
       </c>
       <c r="H45" s="3">
-        <v>28800</v>
+        <v>26500</v>
       </c>
       <c r="I45" s="3">
-        <v>27000</v>
+        <v>29000</v>
       </c>
       <c r="J45" s="3">
+        <v>27200</v>
+      </c>
+      <c r="K45" s="3">
         <v>19700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>18600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>23300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>17800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>34500</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2590,47 +2689,50 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>424600</v>
+        <v>324800</v>
       </c>
       <c r="E46" s="3">
-        <v>500700</v>
+        <v>427500</v>
       </c>
       <c r="F46" s="3">
-        <v>595800</v>
+        <v>504200</v>
       </c>
       <c r="G46" s="3">
-        <v>660300</v>
+        <v>599800</v>
       </c>
       <c r="H46" s="3">
-        <v>720200</v>
+        <v>664800</v>
       </c>
       <c r="I46" s="3">
-        <v>737900</v>
+        <v>725100</v>
       </c>
       <c r="J46" s="3">
+        <v>742900</v>
+      </c>
+      <c r="K46" s="3">
         <v>443000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>240700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>195500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>216600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>253100</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2646,35 +2748,38 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E47" s="3">
         <v>1600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4300</v>
       </c>
-      <c r="F47" s="3">
-        <v>30100</v>
-      </c>
       <c r="G47" s="3">
-        <v>48600</v>
+        <v>30300</v>
       </c>
       <c r="H47" s="3">
-        <v>79800</v>
+        <v>48900</v>
       </c>
       <c r="I47" s="3">
-        <v>91800</v>
+        <v>80400</v>
       </c>
       <c r="J47" s="3">
+        <v>92400</v>
+      </c>
+      <c r="K47" s="3">
         <v>105400</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2687,8 +2792,8 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -2702,47 +2807,50 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>14100</v>
+        <v>11500</v>
       </c>
       <c r="E48" s="3">
-        <v>17100</v>
+        <v>14200</v>
       </c>
       <c r="F48" s="3">
-        <v>22400</v>
+        <v>17200</v>
       </c>
       <c r="G48" s="3">
-        <v>21900</v>
+        <v>22500</v>
       </c>
       <c r="H48" s="3">
-        <v>9000</v>
+        <v>22000</v>
       </c>
       <c r="I48" s="3">
+        <v>9100</v>
+      </c>
+      <c r="J48" s="3">
         <v>5600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6200</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2758,47 +2866,50 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>38800</v>
+        <v>16400</v>
       </c>
       <c r="E49" s="3">
-        <v>38900</v>
+        <v>39100</v>
       </c>
       <c r="F49" s="3">
-        <v>38900</v>
+        <v>39100</v>
       </c>
       <c r="G49" s="3">
-        <v>39000</v>
+        <v>39200</v>
       </c>
       <c r="H49" s="3">
-        <v>39000</v>
+        <v>39200</v>
       </c>
       <c r="I49" s="3">
-        <v>39100</v>
+        <v>39300</v>
       </c>
       <c r="J49" s="3">
         <v>39300</v>
       </c>
       <c r="K49" s="3">
+        <v>39300</v>
+      </c>
+      <c r="L49" s="3">
         <v>44300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>44700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>45500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>49100</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2814,8 +2925,11 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2870,8 +2984,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2926,44 +3043,47 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>600</v>
+      </c>
+      <c r="E52" s="3">
         <v>5800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3700</v>
       </c>
-      <c r="H52" s="3">
-        <v>800</v>
-      </c>
       <c r="I52" s="3">
+        <v>900</v>
+      </c>
+      <c r="J52" s="3">
         <v>300</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
       <c r="K52" s="3">
         <v>0</v>
       </c>
       <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
         <v>2600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>900</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2982,8 +3102,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3038,47 +3161,50 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>484900</v>
+        <v>363300</v>
       </c>
       <c r="E54" s="3">
-        <v>562500</v>
+        <v>488200</v>
       </c>
       <c r="F54" s="3">
-        <v>689200</v>
+        <v>566300</v>
       </c>
       <c r="G54" s="3">
-        <v>773400</v>
+        <v>693900</v>
       </c>
       <c r="H54" s="3">
-        <v>848900</v>
+        <v>778700</v>
       </c>
       <c r="I54" s="3">
-        <v>874600</v>
+        <v>854700</v>
       </c>
       <c r="J54" s="3">
+        <v>880500</v>
+      </c>
+      <c r="K54" s="3">
         <v>593500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>291200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>249600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>268600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>308500</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3094,8 +3220,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3116,8 +3245,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3138,38 +3268,39 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>82200</v>
+        <v>49700</v>
       </c>
       <c r="E57" s="3">
-        <v>97600</v>
+        <v>82700</v>
       </c>
       <c r="F57" s="3">
-        <v>75600</v>
+        <v>98200</v>
       </c>
       <c r="G57" s="3">
-        <v>81900</v>
+        <v>76100</v>
       </c>
       <c r="H57" s="3">
-        <v>74000</v>
+        <v>82500</v>
       </c>
       <c r="I57" s="3">
-        <v>77400</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K57" s="3">
+        <v>74500</v>
+      </c>
+      <c r="J57" s="3">
+        <v>77900</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3">
         <v>34600</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3185,8 +3316,8 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R57" s="3">
-        <v>0</v>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S57" s="3">
         <v>0</v>
@@ -3194,22 +3325,25 @@
       <c r="T57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4100</v>
+        <v>4200</v>
       </c>
       <c r="E58" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F58" s="3">
         <v>2600</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
+      <c r="G58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -3224,17 +3358,17 @@
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>7200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7900</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3250,47 +3384,50 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5200</v>
+        <v>3300</v>
       </c>
       <c r="E59" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F59" s="3">
         <v>4500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5900</v>
       </c>
-      <c r="G59" s="3">
-        <v>4200</v>
-      </c>
       <c r="H59" s="3">
+        <v>4300</v>
+      </c>
+      <c r="I59" s="3">
         <v>2000</v>
       </c>
-      <c r="I59" s="3">
-        <v>2100</v>
-      </c>
       <c r="J59" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K59" s="3">
         <v>48200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>77300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>61400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>57300</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3306,47 +3443,50 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>91600</v>
+        <v>57300</v>
       </c>
       <c r="E60" s="3">
-        <v>104700</v>
+        <v>92200</v>
       </c>
       <c r="F60" s="3">
-        <v>81500</v>
+        <v>105400</v>
       </c>
       <c r="G60" s="3">
-        <v>86200</v>
+        <v>82000</v>
       </c>
       <c r="H60" s="3">
-        <v>76000</v>
+        <v>86700</v>
       </c>
       <c r="I60" s="3">
-        <v>79600</v>
+        <v>76500</v>
       </c>
       <c r="J60" s="3">
+        <v>80100</v>
+      </c>
+      <c r="K60" s="3">
         <v>48200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>35700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>84500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>68700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>65200</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3362,8 +3502,11 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3386,23 +3529,23 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>8900</v>
-      </c>
-      <c r="K61" s="3">
-        <v>9800</v>
       </c>
       <c r="L61" s="3">
         <v>9800</v>
       </c>
       <c r="M61" s="3">
+        <v>9800</v>
+      </c>
+      <c r="N61" s="3">
         <v>10300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10600</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3418,47 +3561,50 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>55500</v>
+        <v>67100</v>
       </c>
       <c r="E62" s="3">
-        <v>56000</v>
+        <v>55900</v>
       </c>
       <c r="F62" s="3">
-        <v>53200</v>
+        <v>56400</v>
       </c>
       <c r="G62" s="3">
-        <v>57700</v>
+        <v>53600</v>
       </c>
       <c r="H62" s="3">
-        <v>19000</v>
+        <v>58100</v>
       </c>
       <c r="I62" s="3">
-        <v>18000</v>
+        <v>19100</v>
       </c>
       <c r="J62" s="3">
+        <v>18100</v>
+      </c>
+      <c r="K62" s="3">
         <v>19600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1600</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3474,8 +3620,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3530,8 +3679,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3586,8 +3738,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3642,47 +3797,50 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>147000</v>
+        <v>124400</v>
       </c>
       <c r="E66" s="3">
-        <v>160700</v>
+        <v>148000</v>
       </c>
       <c r="F66" s="3">
-        <v>134700</v>
+        <v>161800</v>
       </c>
       <c r="G66" s="3">
-        <v>143800</v>
+        <v>135600</v>
       </c>
       <c r="H66" s="3">
-        <v>95000</v>
+        <v>144800</v>
       </c>
       <c r="I66" s="3">
-        <v>97600</v>
+        <v>95700</v>
       </c>
       <c r="J66" s="3">
+        <v>98200</v>
+      </c>
+      <c r="K66" s="3">
         <v>76800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>49000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>96000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>80300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>77500</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3698,8 +3856,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3720,8 +3881,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3776,8 +3938,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3832,8 +3997,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3862,17 +4030,17 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
         <v>445800</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>425700</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>459900</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
@@ -3888,8 +4056,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3944,47 +4115,50 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-1054200</v>
+        <v>-1157700</v>
       </c>
       <c r="E72" s="3">
-        <v>-947500</v>
+        <v>-1061400</v>
       </c>
       <c r="F72" s="3">
-        <v>-745900</v>
+        <v>-954000</v>
       </c>
       <c r="G72" s="3">
-        <v>-601300</v>
+        <v>-750900</v>
       </c>
       <c r="H72" s="3">
-        <v>-428000</v>
+        <v>-605400</v>
       </c>
       <c r="I72" s="3">
-        <v>-279400</v>
+        <v>-430900</v>
       </c>
       <c r="J72" s="3">
+        <v>-281300</v>
+      </c>
+      <c r="K72" s="3">
         <v>-423200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-437400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-358200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-309300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-295300</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4000,8 +4174,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4056,8 +4233,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4112,8 +4292,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4168,47 +4351,50 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>337900</v>
+        <v>238900</v>
       </c>
       <c r="E76" s="3">
-        <v>401800</v>
+        <v>340200</v>
       </c>
       <c r="F76" s="3">
-        <v>554500</v>
+        <v>404500</v>
       </c>
       <c r="G76" s="3">
-        <v>629600</v>
+        <v>558300</v>
       </c>
       <c r="H76" s="3">
-        <v>753900</v>
+        <v>633900</v>
       </c>
       <c r="I76" s="3">
-        <v>777000</v>
+        <v>759000</v>
       </c>
       <c r="J76" s="3">
+        <v>782300</v>
+      </c>
+      <c r="K76" s="3">
         <v>516600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>242200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-292200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-237300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-228900</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4224,8 +4410,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4280,125 +4469,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44196</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44104</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44012</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43830</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43738</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43646</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43465</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43373</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43281</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>-106700</v>
+      <c r="D81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E81" s="3">
-        <v>-201700</v>
+        <v>-107400</v>
       </c>
       <c r="F81" s="3">
-        <v>-144600</v>
+        <v>-203000</v>
       </c>
       <c r="G81" s="3">
-        <v>-173300</v>
+        <v>-145500</v>
       </c>
       <c r="H81" s="3">
-        <v>-148600</v>
+        <v>-174500</v>
       </c>
       <c r="I81" s="3">
-        <v>145500</v>
+        <v>-149700</v>
       </c>
       <c r="J81" s="3">
+        <v>146500</v>
+      </c>
+      <c r="K81" s="3">
         <v>1700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-82900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-213300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-35900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-135300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-62000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-17200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-25500</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4419,8 +4617,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4439,30 +4638,30 @@
       <c r="H83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3">
         <v>2000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1100</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3">
         <v>1400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1000</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4475,8 +4674,11 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4531,8 +4733,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4587,8 +4792,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4643,8 +4851,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4699,8 +4910,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4755,8 +4969,11 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4775,30 +4992,30 @@
       <c r="H89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I89" s="3">
-        <v>59900</v>
+      <c r="I89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J89" s="3">
+        <v>60300</v>
+      </c>
+      <c r="K89" s="3">
         <v>-80400</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3">
         <v>-124700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-95200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-61400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-43200</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4811,8 +5028,11 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4833,8 +5053,9 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4863,20 +5084,20 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-1800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2200</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4889,8 +5110,11 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4945,8 +5169,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5001,8 +5228,11 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5021,30 +5251,30 @@
       <c r="H94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I94" s="3">
-        <v>-27900</v>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J94" s="3">
+        <v>-28100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-35400</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3">
         <v>30500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>19700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>24900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1500</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5057,8 +5287,11 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5079,8 +5312,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5135,8 +5369,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5191,8 +5428,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5247,8 +5487,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5303,8 +5546,11 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5323,30 +5569,30 @@
       <c r="H100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I100" s="3">
-        <v>475100</v>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J100" s="3">
+        <v>478300</v>
+      </c>
+      <c r="K100" s="3">
         <v>358400</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3">
         <v>21900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>5800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>227800</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5359,8 +5605,11 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5379,30 +5628,30 @@
       <c r="H101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I101" s="3">
-        <v>-14700</v>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J101" s="3">
+        <v>-14800</v>
+      </c>
+      <c r="K101" s="3">
         <v>1400</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3">
         <v>2200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>11300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>9200</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5415,8 +5664,11 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5435,30 +5687,30 @@
       <c r="H102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I102" s="3">
-        <v>492300</v>
+      <c r="I102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J102" s="3">
+        <v>495700</v>
+      </c>
+      <c r="K102" s="3">
         <v>244000</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3">
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3">
         <v>-70000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-58400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-41700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>195300</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5469,6 +5721,9 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IMAB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IMAB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="92">
   <si>
     <t>IMAB</t>
   </si>
@@ -752,7 +752,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>3800</v>
+        <v>1100</v>
       </c>
       <c r="E8" s="3">
         <v>2700</v>
@@ -764,13 +764,13 @@
         <v>7200</v>
       </c>
       <c r="H8" s="3">
-        <v>9800</v>
+        <v>9700</v>
       </c>
       <c r="I8" s="3">
         <v>2500</v>
       </c>
       <c r="J8" s="3">
-        <v>214500</v>
+        <v>213100</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -823,7 +823,7 @@
         <v>3800</v>
       </c>
       <c r="H9" s="3">
-        <v>6500</v>
+        <v>6400</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
@@ -952,25 +952,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>112700</v>
+        <v>50300</v>
       </c>
       <c r="E12" s="3">
-        <v>62100</v>
+        <v>61700</v>
       </c>
       <c r="F12" s="3">
-        <v>62900</v>
+        <v>62500</v>
       </c>
       <c r="G12" s="3">
-        <v>62900</v>
+        <v>62500</v>
       </c>
       <c r="H12" s="3">
-        <v>86200</v>
+        <v>85700</v>
       </c>
       <c r="I12" s="3">
-        <v>82400</v>
+        <v>81900</v>
       </c>
       <c r="J12" s="3">
-        <v>75400</v>
+        <v>74900</v>
       </c>
       <c r="K12" s="3">
         <v>35400</v>
@@ -1069,8 +1069,8 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>22500</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1207,26 +1207,26 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>3</v>
+      <c r="D17" s="3">
+        <v>101500</v>
       </c>
       <c r="E17" s="3">
-        <v>96100</v>
+        <v>95500</v>
       </c>
       <c r="F17" s="3">
-        <v>121700</v>
+        <v>121000</v>
       </c>
       <c r="G17" s="3">
-        <v>121300</v>
+        <v>120500</v>
       </c>
       <c r="H17" s="3">
-        <v>155000</v>
+        <v>154000</v>
       </c>
       <c r="I17" s="3">
-        <v>145200</v>
+        <v>144300</v>
       </c>
       <c r="J17" s="3">
-        <v>107500</v>
+        <v>106900</v>
       </c>
       <c r="K17" s="3">
         <v>54600</v>
@@ -1266,26 +1266,26 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-100400</v>
       </c>
       <c r="E18" s="3">
-        <v>-93400</v>
+        <v>-92800</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G18" s="3">
-        <v>-114100</v>
+        <v>-113300</v>
       </c>
       <c r="H18" s="3">
-        <v>-145200</v>
+        <v>-144300</v>
       </c>
       <c r="I18" s="3">
-        <v>-142700</v>
+        <v>-141800</v>
       </c>
       <c r="J18" s="3">
-        <v>106900</v>
+        <v>106300</v>
       </c>
       <c r="K18" s="3">
         <v>-54600</v>
@@ -1348,26 +1348,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>4800</v>
       </c>
       <c r="E20" s="3">
-        <v>-14000</v>
+        <v>-13900</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G20" s="3">
-        <v>-31500</v>
+        <v>-31300</v>
       </c>
       <c r="H20" s="3">
-        <v>-29300</v>
+        <v>-29100</v>
       </c>
       <c r="I20" s="3">
-        <v>-7400</v>
+        <v>-7300</v>
       </c>
       <c r="J20" s="3">
-        <v>41300</v>
+        <v>41000</v>
       </c>
       <c r="K20" s="3">
         <v>56300</v>
@@ -1426,7 +1426,7 @@
         <v>3</v>
       </c>
       <c r="J21" s="3">
-        <v>150200</v>
+        <v>149300</v>
       </c>
       <c r="K21" s="3">
         <v>2800</v>
@@ -1526,25 +1526,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-203800</v>
+        <v>-95700</v>
       </c>
       <c r="E23" s="3">
-        <v>-107400</v>
+        <v>-106800</v>
       </c>
       <c r="F23" s="3">
-        <v>-202900</v>
+        <v>-201700</v>
       </c>
       <c r="G23" s="3">
-        <v>-145500</v>
+        <v>-144600</v>
       </c>
       <c r="H23" s="3">
-        <v>-174500</v>
+        <v>-173400</v>
       </c>
       <c r="I23" s="3">
-        <v>-150100</v>
+        <v>-149200</v>
       </c>
       <c r="J23" s="3">
-        <v>148200</v>
+        <v>147300</v>
       </c>
       <c r="K23" s="3">
         <v>1700</v>
@@ -1702,26 +1702,26 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>-95700</v>
       </c>
       <c r="E26" s="3">
-        <v>-107400</v>
+        <v>-106800</v>
       </c>
       <c r="F26" s="3">
-        <v>-203000</v>
+        <v>-201800</v>
       </c>
       <c r="G26" s="3">
-        <v>-145500</v>
+        <v>-144600</v>
       </c>
       <c r="H26" s="3">
-        <v>-174500</v>
+        <v>-173400</v>
       </c>
       <c r="I26" s="3">
-        <v>-149700</v>
+        <v>-148700</v>
       </c>
       <c r="J26" s="3">
-        <v>146500</v>
+        <v>145600</v>
       </c>
       <c r="K26" s="3">
         <v>1700</v>
@@ -1761,26 +1761,26 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>-95700</v>
       </c>
       <c r="E27" s="3">
-        <v>-107400</v>
+        <v>-106800</v>
       </c>
       <c r="F27" s="3">
-        <v>-203000</v>
+        <v>-201800</v>
       </c>
       <c r="G27" s="3">
-        <v>-145500</v>
+        <v>-144600</v>
       </c>
       <c r="H27" s="3">
-        <v>-174500</v>
+        <v>-173400</v>
       </c>
       <c r="I27" s="3">
-        <v>-149700</v>
+        <v>-148700</v>
       </c>
       <c r="J27" s="3">
-        <v>146500</v>
+        <v>145600</v>
       </c>
       <c r="K27" s="3">
         <v>1700</v>
@@ -2056,26 +2056,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-4800</v>
       </c>
       <c r="E32" s="3">
-        <v>14000</v>
+        <v>13900</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G32" s="3">
-        <v>31500</v>
+        <v>31300</v>
       </c>
       <c r="H32" s="3">
-        <v>29300</v>
+        <v>29100</v>
       </c>
       <c r="I32" s="3">
-        <v>7400</v>
+        <v>7300</v>
       </c>
       <c r="J32" s="3">
-        <v>-41300</v>
+        <v>-41000</v>
       </c>
       <c r="K32" s="3">
         <v>-56300</v>
@@ -2115,26 +2115,26 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>-95700</v>
       </c>
       <c r="E33" s="3">
-        <v>-107400</v>
+        <v>-106800</v>
       </c>
       <c r="F33" s="3">
-        <v>-203000</v>
+        <v>-201800</v>
       </c>
       <c r="G33" s="3">
-        <v>-145500</v>
+        <v>-144600</v>
       </c>
       <c r="H33" s="3">
-        <v>-174500</v>
+        <v>-173400</v>
       </c>
       <c r="I33" s="3">
-        <v>-149700</v>
+        <v>-148700</v>
       </c>
       <c r="J33" s="3">
-        <v>146500</v>
+        <v>145600</v>
       </c>
       <c r="K33" s="3">
         <v>1700</v>
@@ -2233,26 +2233,26 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>-95700</v>
       </c>
       <c r="E35" s="3">
-        <v>-107400</v>
+        <v>-106800</v>
       </c>
       <c r="F35" s="3">
-        <v>-203000</v>
+        <v>-201800</v>
       </c>
       <c r="G35" s="3">
-        <v>-145500</v>
+        <v>-144600</v>
       </c>
       <c r="H35" s="3">
-        <v>-174500</v>
+        <v>-173400</v>
       </c>
       <c r="I35" s="3">
-        <v>-149700</v>
+        <v>-148700</v>
       </c>
       <c r="J35" s="3">
-        <v>146500</v>
+        <v>145600</v>
       </c>
       <c r="K35" s="3">
         <v>1700</v>
@@ -2403,25 +2403,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>297700</v>
+        <v>295900</v>
       </c>
       <c r="E41" s="3">
-        <v>328000</v>
+        <v>326000</v>
       </c>
       <c r="F41" s="3">
-        <v>446800</v>
+        <v>444000</v>
       </c>
       <c r="G41" s="3">
-        <v>515900</v>
+        <v>512700</v>
       </c>
       <c r="H41" s="3">
-        <v>489900</v>
+        <v>486800</v>
       </c>
       <c r="I41" s="3">
-        <v>603600</v>
+        <v>599900</v>
       </c>
       <c r="J41" s="3">
-        <v>661600</v>
+        <v>657500</v>
       </c>
       <c r="K41" s="3">
         <v>408700</v>
@@ -2462,22 +2462,22 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>19900</v>
+        <v>19800</v>
       </c>
       <c r="E42" s="3">
-        <v>81500</v>
+        <v>80900</v>
       </c>
       <c r="F42" s="3">
-        <v>32700</v>
+        <v>32500</v>
       </c>
       <c r="G42" s="3">
-        <v>29400</v>
+        <v>29200</v>
       </c>
       <c r="H42" s="3">
-        <v>104700</v>
+        <v>104100</v>
       </c>
       <c r="I42" s="3">
-        <v>58700</v>
+        <v>58400</v>
       </c>
       <c r="J42" s="3">
         <v>4400</v>
@@ -2530,16 +2530,16 @@
         <v>0</v>
       </c>
       <c r="G43" s="3">
-        <v>40500</v>
+        <v>40300</v>
       </c>
       <c r="H43" s="3">
-        <v>39900</v>
+        <v>39600</v>
       </c>
       <c r="I43" s="3">
-        <v>33800</v>
+        <v>33600</v>
       </c>
       <c r="J43" s="3">
-        <v>49800</v>
+        <v>49400</v>
       </c>
       <c r="K43" s="3">
         <v>10700</v>
@@ -2642,22 +2642,22 @@
         <v>7200</v>
       </c>
       <c r="E45" s="3">
-        <v>18000</v>
+        <v>17900</v>
       </c>
       <c r="F45" s="3">
-        <v>24600</v>
+        <v>24500</v>
       </c>
       <c r="G45" s="3">
         <v>14000</v>
       </c>
       <c r="H45" s="3">
-        <v>26500</v>
+        <v>26400</v>
       </c>
       <c r="I45" s="3">
-        <v>29000</v>
+        <v>28800</v>
       </c>
       <c r="J45" s="3">
-        <v>27200</v>
+        <v>27000</v>
       </c>
       <c r="K45" s="3">
         <v>19700</v>
@@ -2698,25 +2698,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>324800</v>
+        <v>322800</v>
       </c>
       <c r="E46" s="3">
-        <v>427500</v>
+        <v>424800</v>
       </c>
       <c r="F46" s="3">
-        <v>504200</v>
+        <v>501000</v>
       </c>
       <c r="G46" s="3">
-        <v>599800</v>
+        <v>596100</v>
       </c>
       <c r="H46" s="3">
-        <v>664800</v>
+        <v>660600</v>
       </c>
       <c r="I46" s="3">
-        <v>725100</v>
+        <v>720600</v>
       </c>
       <c r="J46" s="3">
-        <v>742900</v>
+        <v>738300</v>
       </c>
       <c r="K46" s="3">
         <v>443000</v>
@@ -2766,16 +2766,16 @@
         <v>4300</v>
       </c>
       <c r="G47" s="3">
-        <v>30300</v>
+        <v>30100</v>
       </c>
       <c r="H47" s="3">
-        <v>48900</v>
+        <v>48600</v>
       </c>
       <c r="I47" s="3">
-        <v>80400</v>
+        <v>79900</v>
       </c>
       <c r="J47" s="3">
-        <v>92400</v>
+        <v>91900</v>
       </c>
       <c r="K47" s="3">
         <v>105400</v>
@@ -2822,16 +2822,16 @@
         <v>14200</v>
       </c>
       <c r="F48" s="3">
-        <v>17200</v>
+        <v>17100</v>
       </c>
       <c r="G48" s="3">
-        <v>22500</v>
+        <v>22400</v>
       </c>
       <c r="H48" s="3">
-        <v>22000</v>
+        <v>21900</v>
       </c>
       <c r="I48" s="3">
-        <v>9100</v>
+        <v>9000</v>
       </c>
       <c r="J48" s="3">
         <v>5600</v>
@@ -2875,25 +2875,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>16400</v>
+        <v>16300</v>
       </c>
       <c r="E49" s="3">
+        <v>38800</v>
+      </c>
+      <c r="F49" s="3">
+        <v>38900</v>
+      </c>
+      <c r="G49" s="3">
+        <v>38900</v>
+      </c>
+      <c r="H49" s="3">
+        <v>39000</v>
+      </c>
+      <c r="I49" s="3">
+        <v>39000</v>
+      </c>
+      <c r="J49" s="3">
         <v>39100</v>
-      </c>
-      <c r="F49" s="3">
-        <v>39100</v>
-      </c>
-      <c r="G49" s="3">
-        <v>39200</v>
-      </c>
-      <c r="H49" s="3">
-        <v>39200</v>
-      </c>
-      <c r="I49" s="3">
-        <v>39300</v>
-      </c>
-      <c r="J49" s="3">
-        <v>39300</v>
       </c>
       <c r="K49" s="3">
         <v>39300</v>
@@ -3052,7 +3052,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>600</v>
+        <v>8700</v>
       </c>
       <c r="E52" s="3">
         <v>5800</v>
@@ -3067,7 +3067,7 @@
         <v>3700</v>
       </c>
       <c r="I52" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="J52" s="3">
         <v>300</v>
@@ -3170,25 +3170,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>363300</v>
+        <v>361000</v>
       </c>
       <c r="E54" s="3">
-        <v>488200</v>
+        <v>485200</v>
       </c>
       <c r="F54" s="3">
-        <v>566300</v>
+        <v>562800</v>
       </c>
       <c r="G54" s="3">
-        <v>693900</v>
+        <v>689600</v>
       </c>
       <c r="H54" s="3">
-        <v>778700</v>
+        <v>773900</v>
       </c>
       <c r="I54" s="3">
-        <v>854700</v>
+        <v>849400</v>
       </c>
       <c r="J54" s="3">
-        <v>880500</v>
+        <v>875100</v>
       </c>
       <c r="K54" s="3">
         <v>593500</v>
@@ -3275,25 +3275,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>49700</v>
+        <v>49400</v>
       </c>
       <c r="E57" s="3">
-        <v>82700</v>
+        <v>82200</v>
       </c>
       <c r="F57" s="3">
-        <v>98200</v>
+        <v>97600</v>
       </c>
       <c r="G57" s="3">
-        <v>76100</v>
+        <v>75600</v>
       </c>
       <c r="H57" s="3">
-        <v>82500</v>
+        <v>82000</v>
       </c>
       <c r="I57" s="3">
-        <v>74500</v>
+        <v>74100</v>
       </c>
       <c r="J57" s="3">
-        <v>77900</v>
+        <v>77400</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -3334,10 +3334,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4200</v>
+        <v>4100</v>
       </c>
       <c r="E58" s="3">
-        <v>4200</v>
+        <v>4100</v>
       </c>
       <c r="F58" s="3">
         <v>2600</v>
@@ -3396,7 +3396,7 @@
         <v>3300</v>
       </c>
       <c r="E59" s="3">
-        <v>5300</v>
+        <v>5200</v>
       </c>
       <c r="F59" s="3">
         <v>4500</v>
@@ -3405,7 +3405,7 @@
         <v>5900</v>
       </c>
       <c r="H59" s="3">
-        <v>4300</v>
+        <v>4200</v>
       </c>
       <c r="I59" s="3">
         <v>2000</v>
@@ -3452,25 +3452,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>57300</v>
+        <v>56900</v>
       </c>
       <c r="E60" s="3">
-        <v>92200</v>
+        <v>91600</v>
       </c>
       <c r="F60" s="3">
-        <v>105400</v>
+        <v>104700</v>
       </c>
       <c r="G60" s="3">
-        <v>82000</v>
+        <v>81500</v>
       </c>
       <c r="H60" s="3">
-        <v>86700</v>
+        <v>86200</v>
       </c>
       <c r="I60" s="3">
-        <v>76500</v>
+        <v>76100</v>
       </c>
       <c r="J60" s="3">
-        <v>80100</v>
+        <v>79600</v>
       </c>
       <c r="K60" s="3">
         <v>48200</v>
@@ -3570,25 +3570,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>67100</v>
+        <v>66700</v>
       </c>
       <c r="E62" s="3">
-        <v>55900</v>
+        <v>55500</v>
       </c>
       <c r="F62" s="3">
-        <v>56400</v>
+        <v>56000</v>
       </c>
       <c r="G62" s="3">
-        <v>53600</v>
+        <v>53300</v>
       </c>
       <c r="H62" s="3">
-        <v>58100</v>
+        <v>57700</v>
       </c>
       <c r="I62" s="3">
-        <v>19100</v>
+        <v>19000</v>
       </c>
       <c r="J62" s="3">
-        <v>18100</v>
+        <v>18000</v>
       </c>
       <c r="K62" s="3">
         <v>19600</v>
@@ -3806,25 +3806,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>124400</v>
+        <v>123600</v>
       </c>
       <c r="E66" s="3">
-        <v>148000</v>
+        <v>147100</v>
       </c>
       <c r="F66" s="3">
-        <v>161800</v>
+        <v>160800</v>
       </c>
       <c r="G66" s="3">
-        <v>135600</v>
+        <v>134800</v>
       </c>
       <c r="H66" s="3">
-        <v>144800</v>
+        <v>143900</v>
       </c>
       <c r="I66" s="3">
-        <v>95700</v>
+        <v>95100</v>
       </c>
       <c r="J66" s="3">
-        <v>98200</v>
+        <v>97600</v>
       </c>
       <c r="K66" s="3">
         <v>76800</v>
@@ -4124,25 +4124,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-1157700</v>
+        <v>-1150600</v>
       </c>
       <c r="E72" s="3">
-        <v>-1061400</v>
+        <v>-1054800</v>
       </c>
       <c r="F72" s="3">
-        <v>-954000</v>
+        <v>-948100</v>
       </c>
       <c r="G72" s="3">
-        <v>-750900</v>
+        <v>-746300</v>
       </c>
       <c r="H72" s="3">
-        <v>-605400</v>
+        <v>-601700</v>
       </c>
       <c r="I72" s="3">
-        <v>-430900</v>
+        <v>-428300</v>
       </c>
       <c r="J72" s="3">
-        <v>-281300</v>
+        <v>-279500</v>
       </c>
       <c r="K72" s="3">
         <v>-423200</v>
@@ -4360,25 +4360,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>238900</v>
+        <v>237400</v>
       </c>
       <c r="E76" s="3">
-        <v>340200</v>
+        <v>338000</v>
       </c>
       <c r="F76" s="3">
-        <v>404500</v>
+        <v>402000</v>
       </c>
       <c r="G76" s="3">
-        <v>558300</v>
+        <v>554900</v>
       </c>
       <c r="H76" s="3">
-        <v>633900</v>
+        <v>629900</v>
       </c>
       <c r="I76" s="3">
-        <v>759000</v>
+        <v>754300</v>
       </c>
       <c r="J76" s="3">
-        <v>782300</v>
+        <v>777400</v>
       </c>
       <c r="K76" s="3">
         <v>516600</v>
@@ -4541,26 +4541,26 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>-95700</v>
       </c>
       <c r="E81" s="3">
-        <v>-107400</v>
+        <v>-106800</v>
       </c>
       <c r="F81" s="3">
-        <v>-203000</v>
+        <v>-201800</v>
       </c>
       <c r="G81" s="3">
-        <v>-145500</v>
+        <v>-144600</v>
       </c>
       <c r="H81" s="3">
-        <v>-174500</v>
+        <v>-173400</v>
       </c>
       <c r="I81" s="3">
-        <v>-149700</v>
+        <v>-148700</v>
       </c>
       <c r="J81" s="3">
-        <v>146500</v>
+        <v>145600</v>
       </c>
       <c r="K81" s="3">
         <v>1700</v>
@@ -4996,7 +4996,7 @@
         <v>3</v>
       </c>
       <c r="J89" s="3">
-        <v>60300</v>
+        <v>59900</v>
       </c>
       <c r="K89" s="3">
         <v>-80400</v>
@@ -5255,7 +5255,7 @@
         <v>3</v>
       </c>
       <c r="J94" s="3">
-        <v>-28100</v>
+        <v>-27900</v>
       </c>
       <c r="K94" s="3">
         <v>-35400</v>
@@ -5573,7 +5573,7 @@
         <v>3</v>
       </c>
       <c r="J100" s="3">
-        <v>478300</v>
+        <v>475300</v>
       </c>
       <c r="K100" s="3">
         <v>358400</v>
@@ -5632,7 +5632,7 @@
         <v>3</v>
       </c>
       <c r="J101" s="3">
-        <v>-14800</v>
+        <v>-14700</v>
       </c>
       <c r="K101" s="3">
         <v>1400</v>
@@ -5691,7 +5691,7 @@
         <v>3</v>
       </c>
       <c r="J102" s="3">
-        <v>495700</v>
+        <v>492600</v>
       </c>
       <c r="K102" s="3">
         <v>244000</v>

--- a/AAII_Financials/Quarterly/IMAB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IMAB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="92">
   <si>
     <t>IMAB</t>
   </si>
@@ -656,157 +656,164 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44561</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44377</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44196</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44104</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44012</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43830</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43738</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43646</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43465</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43373</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43281</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
-        <v>1100</v>
+      <c r="D8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E8" s="3">
-        <v>2700</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" s="3">
-        <v>7200</v>
+        <v>8000</v>
+      </c>
+      <c r="F8" s="3">
+        <v>19700</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H8" s="3">
-        <v>9700</v>
+        <v>51900</v>
       </c>
       <c r="I8" s="3">
-        <v>2500</v>
+        <v>70300</v>
       </c>
       <c r="J8" s="3">
+        <v>17800</v>
+      </c>
+      <c r="K8" s="3">
         <v>213100</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
       <c r="L8" s="3">
         <v>0</v>
       </c>
       <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
         <v>4300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3300</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -819,14 +826,14 @@
       <c r="F9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G9" s="3">
-        <v>3800</v>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H9" s="3">
-        <v>6400</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
+        <v>27200</v>
+      </c>
+      <c r="I9" s="3">
+        <v>46400</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
@@ -864,8 +871,11 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -878,14 +888,14 @@
       <c r="F10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G10" s="3">
-        <v>3400</v>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H10" s="3">
-        <v>3300</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
+        <v>24700</v>
+      </c>
+      <c r="I10" s="3">
+        <v>23900</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
@@ -923,8 +933,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -946,67 +959,71 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>50300</v>
+        <v>3100</v>
       </c>
       <c r="E12" s="3">
-        <v>61700</v>
+        <v>364200</v>
       </c>
       <c r="F12" s="3">
-        <v>62500</v>
+        <v>446400</v>
       </c>
       <c r="G12" s="3">
-        <v>62500</v>
+        <v>452300</v>
       </c>
       <c r="H12" s="3">
-        <v>85700</v>
+        <v>452600</v>
       </c>
       <c r="I12" s="3">
-        <v>81900</v>
+        <v>620000</v>
       </c>
       <c r="J12" s="3">
+        <v>593000</v>
+      </c>
+      <c r="K12" s="3">
         <v>74900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>35400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>62900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>120700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>45800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>41800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>65600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>17100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>31000</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1064,16 +1081,19 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>22500</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
+        <v>162600</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -1096,12 +1116,12 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>3300</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1117,14 +1137,17 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1182,8 +1205,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1202,126 +1228,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>101500</v>
+        <v>15000</v>
       </c>
       <c r="E17" s="3">
-        <v>95500</v>
+        <v>734800</v>
       </c>
       <c r="F17" s="3">
-        <v>121000</v>
+        <v>691400</v>
       </c>
       <c r="G17" s="3">
-        <v>120500</v>
+        <v>875600</v>
       </c>
       <c r="H17" s="3">
-        <v>154000</v>
+        <v>872300</v>
       </c>
       <c r="I17" s="3">
-        <v>144300</v>
+        <v>1114800</v>
       </c>
       <c r="J17" s="3">
+        <v>1044500</v>
+      </c>
+      <c r="K17" s="3">
         <v>106900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>54600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>87200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>218000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>46900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>132500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>75800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>20500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>33800</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>-100400</v>
+      <c r="D18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E18" s="3">
-        <v>-92800</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-113300</v>
+        <v>-726800</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-671700</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H18" s="3">
-        <v>-144300</v>
+        <v>-820400</v>
       </c>
       <c r="I18" s="3">
-        <v>-141800</v>
+        <v>-1044500</v>
       </c>
       <c r="J18" s="3">
+        <v>-1026700</v>
+      </c>
+      <c r="K18" s="3">
         <v>106300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-54600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-87200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-213700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-44700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-130100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-67500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-17100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-30600</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1343,67 +1376,71 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>4800</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E20" s="3">
-        <v>-13900</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-31300</v>
+        <v>34400</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-100900</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H20" s="3">
-        <v>-29100</v>
+        <v>-226400</v>
       </c>
       <c r="I20" s="3">
-        <v>-7300</v>
+        <v>-210600</v>
       </c>
       <c r="J20" s="3">
+        <v>-52900</v>
+      </c>
+      <c r="K20" s="3">
         <v>41000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>56300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>5600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>8900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>7600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>6500</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1425,162 +1462,171 @@
       <c r="I21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K21" s="3">
         <v>149300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2800</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>-206700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-34900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-134200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-58900</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3">
         <v>-23900</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3">
+        <v>500</v>
+      </c>
+      <c r="F22" s="3">
+        <v>200</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
+        <v>400</v>
+      </c>
+      <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3">
-        <v>400</v>
-      </c>
-      <c r="N22" s="3">
-        <v>100</v>
-      </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1400</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-95700</v>
+        <v>-6800</v>
       </c>
       <c r="E23" s="3">
-        <v>-106800</v>
+        <v>-692900</v>
       </c>
       <c r="F23" s="3">
-        <v>-201700</v>
+        <v>-772800</v>
       </c>
       <c r="G23" s="3">
-        <v>-144600</v>
+        <v>-1459800</v>
       </c>
       <c r="H23" s="3">
-        <v>-173400</v>
+        <v>-1046900</v>
       </c>
       <c r="I23" s="3">
-        <v>-149200</v>
+        <v>-1255100</v>
       </c>
       <c r="J23" s="3">
+        <v>-1079600</v>
+      </c>
+      <c r="K23" s="3">
         <v>147300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-82900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-208500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-35900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-135300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-61800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-17000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-25500</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1591,23 +1637,23 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G24" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
       <c r="I24" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="K24" s="3">
         <v>1700</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
@@ -1621,16 +1667,16 @@
         <v>0</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
+      <c r="S24" s="3">
+        <v>0</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
@@ -1638,8 +1684,11 @@
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1697,126 +1746,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-95700</v>
+        <v>-6800</v>
       </c>
       <c r="E26" s="3">
-        <v>-106800</v>
+        <v>-692900</v>
       </c>
       <c r="F26" s="3">
-        <v>-201800</v>
+        <v>-772800</v>
       </c>
       <c r="G26" s="3">
-        <v>-144600</v>
+        <v>-1460500</v>
       </c>
       <c r="H26" s="3">
-        <v>-173400</v>
+        <v>-1046900</v>
       </c>
       <c r="I26" s="3">
-        <v>-148700</v>
+        <v>-1255100</v>
       </c>
       <c r="J26" s="3">
+        <v>-1076500</v>
+      </c>
+      <c r="K26" s="3">
         <v>145600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-82900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-208500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-35900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-135300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-62000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-17200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-25500</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-95700</v>
+        <v>-6800</v>
       </c>
       <c r="E27" s="3">
-        <v>-106800</v>
+        <v>-692900</v>
       </c>
       <c r="F27" s="3">
-        <v>-201800</v>
+        <v>-772800</v>
       </c>
       <c r="G27" s="3">
-        <v>-144600</v>
+        <v>-1460500</v>
       </c>
       <c r="H27" s="3">
-        <v>-173400</v>
+        <v>-1046900</v>
       </c>
       <c r="I27" s="3">
-        <v>-148700</v>
+        <v>-1255100</v>
       </c>
       <c r="J27" s="3">
+        <v>-1076500</v>
+      </c>
+      <c r="K27" s="3">
         <v>145600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-82900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-213300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-35900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-135300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-62000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-17200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-25500</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1874,31 +1932,34 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+        <v>31900</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -1933,8 +1994,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1992,8 +2056,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2051,126 +2118,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-4800</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E32" s="3">
-        <v>13900</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="3">
-        <v>31300</v>
+        <v>-34400</v>
+      </c>
+      <c r="F32" s="3">
+        <v>100900</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H32" s="3">
-        <v>29100</v>
+        <v>226400</v>
       </c>
       <c r="I32" s="3">
-        <v>7300</v>
+        <v>210600</v>
       </c>
       <c r="J32" s="3">
+        <v>52900</v>
+      </c>
+      <c r="K32" s="3">
         <v>-41000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-56300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-5600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-8900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-6500</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-95700</v>
+        <v>25100</v>
       </c>
       <c r="E33" s="3">
-        <v>-106800</v>
+        <v>-692900</v>
       </c>
       <c r="F33" s="3">
-        <v>-201800</v>
+        <v>-772800</v>
       </c>
       <c r="G33" s="3">
-        <v>-144600</v>
+        <v>-1460500</v>
       </c>
       <c r="H33" s="3">
-        <v>-173400</v>
+        <v>-1046900</v>
       </c>
       <c r="I33" s="3">
-        <v>-148700</v>
+        <v>-1255100</v>
       </c>
       <c r="J33" s="3">
+        <v>-1076500</v>
+      </c>
+      <c r="K33" s="3">
         <v>145600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-82900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-213300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-35900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-135300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-62000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-17200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-25500</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2228,131 +2304,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-95700</v>
+        <v>25100</v>
       </c>
       <c r="E35" s="3">
-        <v>-106800</v>
+        <v>-692900</v>
       </c>
       <c r="F35" s="3">
-        <v>-201800</v>
+        <v>-772800</v>
       </c>
       <c r="G35" s="3">
-        <v>-144600</v>
+        <v>-1460500</v>
       </c>
       <c r="H35" s="3">
-        <v>-173400</v>
+        <v>-1046900</v>
       </c>
       <c r="I35" s="3">
-        <v>-148700</v>
+        <v>-1255100</v>
       </c>
       <c r="J35" s="3">
+        <v>-1076500</v>
+      </c>
+      <c r="K35" s="3">
         <v>145600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-82900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-213300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-35900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-135300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-62000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-17200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-25500</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44561</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44377</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44196</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44104</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44012</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43830</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43738</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43646</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43465</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43373</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43281</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2374,8 +2459,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2397,50 +2483,51 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>295900</v>
+        <v>152000</v>
       </c>
       <c r="E41" s="3">
-        <v>326000</v>
+        <v>2141400</v>
       </c>
       <c r="F41" s="3">
-        <v>444000</v>
+        <v>2359600</v>
       </c>
       <c r="G41" s="3">
-        <v>512700</v>
+        <v>3214000</v>
       </c>
       <c r="H41" s="3">
-        <v>486800</v>
+        <v>3710900</v>
       </c>
       <c r="I41" s="3">
-        <v>599900</v>
+        <v>3523600</v>
       </c>
       <c r="J41" s="3">
+        <v>4342000</v>
+      </c>
+      <c r="K41" s="3">
         <v>657500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>408700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>221800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>163400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>178800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>200200</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2456,49 +2543,52 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>19800</v>
+        <v>55500</v>
       </c>
       <c r="E42" s="3">
-        <v>80900</v>
+        <v>143200</v>
       </c>
       <c r="F42" s="3">
-        <v>32500</v>
+        <v>585900</v>
       </c>
       <c r="G42" s="3">
-        <v>29200</v>
+        <v>235400</v>
       </c>
       <c r="H42" s="3">
-        <v>104100</v>
+        <v>211200</v>
       </c>
       <c r="I42" s="3">
-        <v>58400</v>
+        <v>753200</v>
       </c>
       <c r="J42" s="3">
+        <v>422300</v>
+      </c>
+      <c r="K42" s="3">
         <v>4400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>7700</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
+      <c r="P42" s="3">
+        <v>0</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
@@ -2515,8 +2605,11 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2526,39 +2619,39 @@
       <c r="E43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F43" s="3">
-        <v>0</v>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G43" s="3">
-        <v>40300</v>
+        <v>0</v>
       </c>
       <c r="H43" s="3">
-        <v>39600</v>
+        <v>291600</v>
       </c>
       <c r="I43" s="3">
-        <v>33600</v>
+        <v>286900</v>
       </c>
       <c r="J43" s="3">
+        <v>242900</v>
+      </c>
+      <c r="K43" s="3">
         <v>49400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10700</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3">
         <v>4200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>18400</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2574,8 +2667,11 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2585,17 +2681,17 @@
       <c r="E44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F44" s="3">
-        <v>0</v>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G44" s="3">
         <v>0</v>
       </c>
       <c r="H44" s="3">
-        <v>3800</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="I44" s="3">
+        <v>27200</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
@@ -2612,8 +2708,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2633,50 +2729,53 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>7200</v>
+        <v>23000</v>
       </c>
       <c r="E45" s="3">
-        <v>17900</v>
+        <v>52000</v>
       </c>
       <c r="F45" s="3">
-        <v>24500</v>
+        <v>129300</v>
       </c>
       <c r="G45" s="3">
-        <v>14000</v>
+        <v>177000</v>
       </c>
       <c r="H45" s="3">
-        <v>26400</v>
+        <v>101000</v>
       </c>
       <c r="I45" s="3">
-        <v>28800</v>
+        <v>190800</v>
       </c>
       <c r="J45" s="3">
+        <v>208500</v>
+      </c>
+      <c r="K45" s="3">
         <v>27000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>19700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>18600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>23300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>17800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>34500</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2692,50 +2791,53 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>322800</v>
+        <v>230500</v>
       </c>
       <c r="E46" s="3">
-        <v>424800</v>
+        <v>2336700</v>
       </c>
       <c r="F46" s="3">
-        <v>501000</v>
+        <v>3074800</v>
       </c>
       <c r="G46" s="3">
-        <v>596100</v>
+        <v>3626500</v>
       </c>
       <c r="H46" s="3">
-        <v>660600</v>
+        <v>4314700</v>
       </c>
       <c r="I46" s="3">
-        <v>720600</v>
+        <v>4781700</v>
       </c>
       <c r="J46" s="3">
+        <v>5215700</v>
+      </c>
+      <c r="K46" s="3">
         <v>738300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>443000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>240700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>195500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>216600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>253100</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2751,38 +2853,41 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1700</v>
+        <v>19000</v>
       </c>
       <c r="E47" s="3">
-        <v>1600</v>
+        <v>12100</v>
       </c>
       <c r="F47" s="3">
-        <v>4300</v>
+        <v>11400</v>
       </c>
       <c r="G47" s="3">
-        <v>30100</v>
+        <v>30900</v>
       </c>
       <c r="H47" s="3">
-        <v>48600</v>
+        <v>217700</v>
       </c>
       <c r="I47" s="3">
-        <v>79900</v>
+        <v>352100</v>
       </c>
       <c r="J47" s="3">
+        <v>578000</v>
+      </c>
+      <c r="K47" s="3">
         <v>91900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>105400</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2795,8 +2900,8 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -2810,50 +2915,53 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>11500</v>
+        <v>3900</v>
       </c>
       <c r="E48" s="3">
-        <v>14200</v>
+        <v>82900</v>
       </c>
       <c r="F48" s="3">
-        <v>17100</v>
+        <v>102500</v>
       </c>
       <c r="G48" s="3">
-        <v>22400</v>
+        <v>124000</v>
       </c>
       <c r="H48" s="3">
-        <v>21900</v>
+        <v>162000</v>
       </c>
       <c r="I48" s="3">
-        <v>9000</v>
+        <v>158500</v>
       </c>
       <c r="J48" s="3">
+        <v>65500</v>
+      </c>
+      <c r="K48" s="3">
         <v>5600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6200</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2869,50 +2977,53 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>16300</v>
+      <c r="D49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E49" s="3">
-        <v>38800</v>
+        <v>118100</v>
       </c>
       <c r="F49" s="3">
-        <v>38900</v>
+        <v>281100</v>
       </c>
       <c r="G49" s="3">
-        <v>38900</v>
+        <v>281500</v>
       </c>
       <c r="H49" s="3">
-        <v>39000</v>
+        <v>281900</v>
       </c>
       <c r="I49" s="3">
-        <v>39000</v>
+        <v>282200</v>
       </c>
       <c r="J49" s="3">
+        <v>282600</v>
+      </c>
+      <c r="K49" s="3">
         <v>39100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>39300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>44300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>44700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>45500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>49100</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2928,8 +3039,11 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2987,8 +3101,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3046,47 +3163,50 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>8700</v>
+        <v>500</v>
       </c>
       <c r="E52" s="3">
-        <v>5800</v>
+        <v>63200</v>
       </c>
       <c r="F52" s="3">
-        <v>1500</v>
+        <v>41900</v>
       </c>
       <c r="G52" s="3">
-        <v>2100</v>
+        <v>10900</v>
       </c>
       <c r="H52" s="3">
-        <v>3700</v>
+        <v>15400</v>
       </c>
       <c r="I52" s="3">
-        <v>800</v>
+        <v>26600</v>
       </c>
       <c r="J52" s="3">
+        <v>6100</v>
+      </c>
+      <c r="K52" s="3">
         <v>300</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
       <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
         <v>2600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>900</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3105,8 +3225,11 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3164,50 +3287,53 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>361000</v>
+        <v>253800</v>
       </c>
       <c r="E54" s="3">
-        <v>485200</v>
+        <v>2613000</v>
       </c>
       <c r="F54" s="3">
-        <v>562800</v>
+        <v>3511700</v>
       </c>
       <c r="G54" s="3">
-        <v>689600</v>
+        <v>4073700</v>
       </c>
       <c r="H54" s="3">
-        <v>773900</v>
+        <v>4991600</v>
       </c>
       <c r="I54" s="3">
-        <v>849400</v>
+        <v>5601200</v>
       </c>
       <c r="J54" s="3">
+        <v>6148000</v>
+      </c>
+      <c r="K54" s="3">
         <v>875100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>593500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>291200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>249600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>268600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>308500</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3223,8 +3349,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3246,8 +3375,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3269,41 +3399,42 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>49400</v>
+        <v>11300</v>
       </c>
       <c r="E57" s="3">
-        <v>82200</v>
+        <v>357800</v>
       </c>
       <c r="F57" s="3">
-        <v>97600</v>
+        <v>595200</v>
       </c>
       <c r="G57" s="3">
-        <v>75600</v>
+        <v>706600</v>
       </c>
       <c r="H57" s="3">
-        <v>82000</v>
+        <v>547500</v>
       </c>
       <c r="I57" s="3">
-        <v>74100</v>
+        <v>593300</v>
       </c>
       <c r="J57" s="3">
+        <v>536200</v>
+      </c>
+      <c r="K57" s="3">
         <v>77400</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3">
         <v>34600</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3319,8 +3450,8 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T57" s="3">
         <v>0</v>
@@ -3328,25 +3459,28 @@
       <c r="U57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>4100</v>
+      <c r="D58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E58" s="3">
-        <v>4100</v>
+        <v>30000</v>
       </c>
       <c r="F58" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
+        <v>30000</v>
+      </c>
+      <c r="G58" s="3">
+        <v>19000</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -3361,17 +3495,17 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>7200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7900</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3387,50 +3521,53 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3300</v>
+        <v>2700</v>
       </c>
       <c r="E59" s="3">
-        <v>5200</v>
+        <v>24100</v>
       </c>
       <c r="F59" s="3">
-        <v>4500</v>
+        <v>37900</v>
       </c>
       <c r="G59" s="3">
-        <v>5900</v>
+        <v>32600</v>
       </c>
       <c r="H59" s="3">
-        <v>4200</v>
+        <v>42500</v>
       </c>
       <c r="I59" s="3">
-        <v>2000</v>
+        <v>30700</v>
       </c>
       <c r="J59" s="3">
+        <v>14500</v>
+      </c>
+      <c r="K59" s="3">
         <v>2200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>48200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>77300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>61400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>57300</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3446,50 +3583,53 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>56900</v>
+        <v>14000</v>
       </c>
       <c r="E60" s="3">
-        <v>91600</v>
+        <v>411800</v>
       </c>
       <c r="F60" s="3">
-        <v>104700</v>
+        <v>663100</v>
       </c>
       <c r="G60" s="3">
-        <v>81500</v>
+        <v>758200</v>
       </c>
       <c r="H60" s="3">
-        <v>86200</v>
+        <v>590000</v>
       </c>
       <c r="I60" s="3">
-        <v>76100</v>
+        <v>624000</v>
       </c>
       <c r="J60" s="3">
+        <v>550600</v>
+      </c>
+      <c r="K60" s="3">
         <v>79600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>48200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>35700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>84500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>68700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>65200</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3505,8 +3645,11 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3532,23 +3675,23 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>8900</v>
-      </c>
-      <c r="L61" s="3">
-        <v>9800</v>
       </c>
       <c r="M61" s="3">
         <v>9800</v>
       </c>
       <c r="N61" s="3">
+        <v>9800</v>
+      </c>
+      <c r="O61" s="3">
         <v>10300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10600</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3564,50 +3707,53 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>66700</v>
+        <v>3200</v>
       </c>
       <c r="E62" s="3">
-        <v>55500</v>
+        <v>483000</v>
       </c>
       <c r="F62" s="3">
-        <v>56000</v>
+        <v>401800</v>
       </c>
       <c r="G62" s="3">
-        <v>53300</v>
+        <v>405600</v>
       </c>
       <c r="H62" s="3">
-        <v>57700</v>
+        <v>385500</v>
       </c>
       <c r="I62" s="3">
-        <v>19000</v>
+        <v>417600</v>
       </c>
       <c r="J62" s="3">
+        <v>137700</v>
+      </c>
+      <c r="K62" s="3">
         <v>18000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>19600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1600</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3623,8 +3769,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3682,8 +3831,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3741,8 +3893,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3800,50 +3955,53 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>123600</v>
+        <v>17200</v>
       </c>
       <c r="E66" s="3">
-        <v>147100</v>
+        <v>894800</v>
       </c>
       <c r="F66" s="3">
-        <v>160800</v>
+        <v>1064900</v>
       </c>
       <c r="G66" s="3">
-        <v>134800</v>
+        <v>1163800</v>
       </c>
       <c r="H66" s="3">
-        <v>143900</v>
+        <v>975500</v>
       </c>
       <c r="I66" s="3">
-        <v>95100</v>
+        <v>1041600</v>
       </c>
       <c r="J66" s="3">
+        <v>688300</v>
+      </c>
+      <c r="K66" s="3">
         <v>97600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>76800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>49000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>96000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>80300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>77500</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3859,8 +4017,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3882,8 +4043,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3941,8 +4103,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4000,8 +4165,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4033,17 +4201,17 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
         <v>445800</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>425700</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>459900</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
@@ -4059,8 +4227,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4118,50 +4289,53 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-1150600</v>
+        <v>-1256500</v>
       </c>
       <c r="E72" s="3">
-        <v>-1054800</v>
+        <v>-8327800</v>
       </c>
       <c r="F72" s="3">
-        <v>-948100</v>
+        <v>-7634900</v>
       </c>
       <c r="G72" s="3">
-        <v>-746300</v>
+        <v>-6862200</v>
       </c>
       <c r="H72" s="3">
-        <v>-601700</v>
+        <v>-5401700</v>
       </c>
       <c r="I72" s="3">
-        <v>-428300</v>
+        <v>-4354800</v>
       </c>
       <c r="J72" s="3">
+        <v>-3099800</v>
+      </c>
+      <c r="K72" s="3">
         <v>-279500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-423200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-437400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-358200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-309300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-295300</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4177,8 +4351,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4236,8 +4413,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4295,8 +4475,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4354,50 +4537,53 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>237400</v>
+        <v>236600</v>
       </c>
       <c r="E76" s="3">
-        <v>338000</v>
+        <v>1718200</v>
       </c>
       <c r="F76" s="3">
-        <v>402000</v>
+        <v>2446800</v>
       </c>
       <c r="G76" s="3">
-        <v>554900</v>
+        <v>2909900</v>
       </c>
       <c r="H76" s="3">
-        <v>629900</v>
+        <v>4016100</v>
       </c>
       <c r="I76" s="3">
-        <v>754300</v>
+        <v>4559600</v>
       </c>
       <c r="J76" s="3">
+        <v>5459700</v>
+      </c>
+      <c r="K76" s="3">
         <v>777400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>516600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>242200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-292200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-237300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-228900</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4413,8 +4599,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4472,131 +4661,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44561</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44377</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44196</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44104</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44012</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43830</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43738</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43646</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43465</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43373</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43281</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-95700</v>
+        <v>25100</v>
       </c>
       <c r="E81" s="3">
-        <v>-106800</v>
+        <v>-692900</v>
       </c>
       <c r="F81" s="3">
-        <v>-201800</v>
+        <v>-772800</v>
       </c>
       <c r="G81" s="3">
-        <v>-144600</v>
+        <v>-1460500</v>
       </c>
       <c r="H81" s="3">
-        <v>-173400</v>
+        <v>-1046900</v>
       </c>
       <c r="I81" s="3">
-        <v>-148700</v>
+        <v>-1255100</v>
       </c>
       <c r="J81" s="3">
+        <v>-1076500</v>
+      </c>
+      <c r="K81" s="3">
         <v>145600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-82900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-213300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-35900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-135300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-62000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-17200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-25500</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4618,8 +4816,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4641,30 +4840,30 @@
       <c r="I83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K83" s="3">
         <v>2000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1100</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3">
         <v>1400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1000</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4677,8 +4876,11 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4736,8 +4938,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4795,8 +5000,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4854,8 +5062,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4913,8 +5124,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4972,8 +5186,11 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4995,30 +5212,30 @@
       <c r="I89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K89" s="3">
         <v>59900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-80400</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3">
         <v>-124700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-95200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-61400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-43200</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5031,8 +5248,11 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5054,13 +5274,14 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-3200</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -5087,20 +5308,20 @@
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-1800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5113,8 +5334,11 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5172,8 +5396,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5231,8 +5458,11 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5254,30 +5484,30 @@
       <c r="I94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K94" s="3">
         <v>-27900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-35400</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3">
         <v>30500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>19700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>24900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1500</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5290,8 +5520,11 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5313,8 +5546,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5372,8 +5606,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5431,8 +5668,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5490,8 +5730,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5549,8 +5792,11 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5572,30 +5818,30 @@
       <c r="I100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3">
         <v>475300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>358400</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
         <v>21900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>5800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>227800</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5608,8 +5854,11 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5631,30 +5880,30 @@
       <c r="I101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K101" s="3">
         <v>-14700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1400</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3">
         <v>2200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>11300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>9200</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5667,8 +5916,11 @@
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5690,30 +5942,30 @@
       <c r="I102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J102" s="3">
+      <c r="J102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K102" s="3">
         <v>492600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>244000</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3">
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3">
         <v>-70000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-58400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-41700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>195300</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5724,6 +5976,9 @@
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IMAB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IMAB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="92">
   <si>
     <t>IMAB</t>
   </si>
@@ -656,164 +656,171 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
-        <v>45291</v>
-      </c>
       <c r="F7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I7" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44377</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44196</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44104</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44012</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43830</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43738</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43646</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43465</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43373</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43281</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
-        <v>8000</v>
-      </c>
-      <c r="F8" s="3">
-        <v>19700</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3">
+        <v>300</v>
       </c>
       <c r="H8" s="3">
-        <v>51900</v>
+        <v>1400</v>
       </c>
       <c r="I8" s="3">
-        <v>70300</v>
-      </c>
-      <c r="J8" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" s="3">
         <v>17800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>213100</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
       <c r="M8" s="3">
         <v>0</v>
       </c>
       <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
         <v>4300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3300</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -829,14 +836,14 @@
       <c r="G9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H9" s="3">
-        <v>27200</v>
-      </c>
-      <c r="I9" s="3">
-        <v>46400</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+      <c r="H9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -874,8 +881,11 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -888,17 +898,17 @@
       <c r="F10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
+      <c r="G10" s="3">
+        <v>300</v>
       </c>
       <c r="H10" s="3">
-        <v>24700</v>
+        <v>1400</v>
       </c>
       <c r="I10" s="3">
-        <v>23900</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+        <v>1400</v>
+      </c>
+      <c r="J10" s="3">
+        <v>-19800</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -936,8 +946,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -960,70 +973,74 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E12" s="3">
         <v>3100</v>
       </c>
-      <c r="E12" s="3">
-        <v>364200</v>
-      </c>
       <c r="F12" s="3">
-        <v>446400</v>
+        <v>5400</v>
       </c>
       <c r="G12" s="3">
-        <v>452300</v>
+        <v>5100</v>
       </c>
       <c r="H12" s="3">
-        <v>452600</v>
+        <v>30800</v>
       </c>
       <c r="I12" s="3">
-        <v>620000</v>
+        <v>32500</v>
       </c>
       <c r="J12" s="3">
+        <v>32800</v>
+      </c>
+      <c r="K12" s="3">
         <v>593000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>74900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>35400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>62900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>120700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>45800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>41800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>65600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>17100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>31000</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,16 +1101,19 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
-        <v>162600</v>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -1107,8 +1127,8 @@
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+      <c r="J14" s="3">
+        <v>1000</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -1119,12 +1139,12 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>3300</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1140,28 +1160,31 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="H15" s="3">
         <v>0</v>
@@ -1170,7 +1193,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1208,8 +1231,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E17" s="3">
         <v>15000</v>
       </c>
-      <c r="E17" s="3">
-        <v>734800</v>
-      </c>
       <c r="F17" s="3">
-        <v>691400</v>
+        <v>12600</v>
       </c>
       <c r="G17" s="3">
-        <v>875600</v>
+        <v>10900</v>
       </c>
       <c r="H17" s="3">
-        <v>872300</v>
+        <v>47700</v>
       </c>
       <c r="I17" s="3">
-        <v>1114800</v>
+        <v>50300</v>
       </c>
       <c r="J17" s="3">
+        <v>63500</v>
+      </c>
+      <c r="K17" s="3">
         <v>1044500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>106900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>54600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>87200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>218000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>46900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>132500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>75800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>20500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>33800</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-12400</v>
       </c>
       <c r="E18" s="3">
-        <v>-726800</v>
+        <v>-15000</v>
       </c>
       <c r="F18" s="3">
-        <v>-671700</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
+        <v>-12600</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-10600</v>
       </c>
       <c r="H18" s="3">
-        <v>-820400</v>
+        <v>-46300</v>
       </c>
       <c r="I18" s="3">
-        <v>-1044500</v>
+        <v>-48900</v>
       </c>
       <c r="J18" s="3">
+        <v>-83300</v>
+      </c>
+      <c r="K18" s="3">
         <v>-1026700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>106300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-54600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-87200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-213700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-44700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-130100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-67500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-17100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-30600</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,286 +1410,299 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>10500</v>
       </c>
       <c r="E20" s="3">
-        <v>34400</v>
+        <v>-5900</v>
       </c>
       <c r="F20" s="3">
-        <v>-100900</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
+        <v>-1400</v>
+      </c>
+      <c r="G20" s="3">
+        <v>100</v>
       </c>
       <c r="H20" s="3">
-        <v>-226400</v>
+        <v>9100</v>
       </c>
       <c r="I20" s="3">
-        <v>-210600</v>
+        <v>9600</v>
       </c>
       <c r="J20" s="3">
+        <v>23000</v>
+      </c>
+      <c r="K20" s="3">
         <v>-52900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>41000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>56300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>4500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>5600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>8900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>7600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>6500</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="D21" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-55400</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-58500</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-105400</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3">
         <v>149300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2800</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>-206700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-34900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-134200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-58900</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3">
         <v>-23900</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E22" s="3">
-        <v>500</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>100</v>
+      </c>
+      <c r="O22" s="3">
+        <v>400</v>
+      </c>
+      <c r="P22" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>300</v>
+      </c>
+      <c r="R22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="S22" s="3">
         <v>200</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3">
-        <v>100</v>
-      </c>
-      <c r="N22" s="3">
-        <v>400</v>
-      </c>
-      <c r="O22" s="3">
-        <v>100</v>
-      </c>
-      <c r="P22" s="3">
-        <v>300</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>1800</v>
-      </c>
-      <c r="R22" s="3">
-        <v>200</v>
-      </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1400</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-6800</v>
+        <v>-20500</v>
       </c>
       <c r="E23" s="3">
-        <v>-692900</v>
+        <v>-7200</v>
       </c>
       <c r="F23" s="3">
-        <v>-772800</v>
+        <v>-9700</v>
       </c>
       <c r="G23" s="3">
-        <v>-1459800</v>
+        <v>-8200</v>
       </c>
       <c r="H23" s="3">
-        <v>-1046900</v>
+        <v>-53300</v>
       </c>
       <c r="I23" s="3">
-        <v>-1255100</v>
+        <v>-56300</v>
       </c>
       <c r="J23" s="3">
+        <v>-105800</v>
+      </c>
+      <c r="K23" s="3">
         <v>-1079600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>147300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-82900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-208500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-35900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-135300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-61800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-17000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-25500</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>700</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J24" s="3">
+        <v>100</v>
+      </c>
+      <c r="K24" s="3">
         <v>-3100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1700</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
@@ -1670,16 +1716,16 @@
         <v>0</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
+      <c r="T24" s="3">
+        <v>0</v>
       </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
@@ -1687,8 +1733,11 @@
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-6800</v>
+        <v>-20500</v>
       </c>
       <c r="E26" s="3">
-        <v>-692900</v>
+        <v>-7200</v>
       </c>
       <c r="F26" s="3">
-        <v>-772800</v>
+        <v>-9700</v>
       </c>
       <c r="G26" s="3">
-        <v>-1460500</v>
+        <v>-8200</v>
       </c>
       <c r="H26" s="3">
-        <v>-1046900</v>
+        <v>-53300</v>
       </c>
       <c r="I26" s="3">
-        <v>-1255100</v>
+        <v>-56300</v>
       </c>
       <c r="J26" s="3">
+        <v>-105900</v>
+      </c>
+      <c r="K26" s="3">
         <v>-1076500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>145600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-82900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-208500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-35900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-135300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-62000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-17200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-25500</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-6800</v>
+        <v>-20500</v>
       </c>
       <c r="E27" s="3">
-        <v>-692900</v>
+        <v>24800</v>
       </c>
       <c r="F27" s="3">
-        <v>-772800</v>
+        <v>2900</v>
       </c>
       <c r="G27" s="3">
-        <v>-1460500</v>
+        <v>-33300</v>
       </c>
       <c r="H27" s="3">
-        <v>-1046900</v>
+        <v>-53300</v>
       </c>
       <c r="I27" s="3">
-        <v>-1255100</v>
+        <v>-56300</v>
       </c>
       <c r="J27" s="3">
+        <v>-105900</v>
+      </c>
+      <c r="K27" s="3">
         <v>-1076500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>145600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-82900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-213300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-35900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-135300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-62000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-17200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-25500</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,34 +1993,37 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>31900</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="F29" s="3">
+        <v>12600</v>
+      </c>
+      <c r="G29" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -1997,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,132 +2188,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-10500</v>
       </c>
       <c r="E32" s="3">
-        <v>-34400</v>
+        <v>5900</v>
       </c>
       <c r="F32" s="3">
-        <v>100900</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
+        <v>1400</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>226400</v>
+        <v>-9100</v>
       </c>
       <c r="I32" s="3">
-        <v>210600</v>
+        <v>-9600</v>
       </c>
       <c r="J32" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="K32" s="3">
         <v>52900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-41000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-56300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-4500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-5600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-8900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-7600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-6500</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>25100</v>
+        <v>-20500</v>
       </c>
       <c r="E33" s="3">
-        <v>-692900</v>
+        <v>24800</v>
       </c>
       <c r="F33" s="3">
-        <v>-772800</v>
+        <v>2900</v>
       </c>
       <c r="G33" s="3">
-        <v>-1460500</v>
+        <v>-33300</v>
       </c>
       <c r="H33" s="3">
-        <v>-1046900</v>
+        <v>-53300</v>
       </c>
       <c r="I33" s="3">
-        <v>-1255100</v>
+        <v>-56300</v>
       </c>
       <c r="J33" s="3">
+        <v>-105900</v>
+      </c>
+      <c r="K33" s="3">
         <v>-1076500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>145600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-82900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-213300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-35900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-135300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-62000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-17200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-25500</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>25100</v>
+        <v>-20500</v>
       </c>
       <c r="E35" s="3">
-        <v>-692900</v>
+        <v>24800</v>
       </c>
       <c r="F35" s="3">
-        <v>-772800</v>
+        <v>2900</v>
       </c>
       <c r="G35" s="3">
-        <v>-1460500</v>
+        <v>-33300</v>
       </c>
       <c r="H35" s="3">
-        <v>-1046900</v>
+        <v>-53300</v>
       </c>
       <c r="I35" s="3">
-        <v>-1255100</v>
+        <v>-56300</v>
       </c>
       <c r="J35" s="3">
+        <v>-105900</v>
+      </c>
+      <c r="K35" s="3">
         <v>-1076500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>145600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-82900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-213300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-35900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-135300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-62000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-17200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-25500</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
-        <v>45291</v>
-      </c>
       <c r="F38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I38" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44377</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44196</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44104</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44012</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43830</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43738</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43646</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43465</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43373</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43281</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,53 +2570,54 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>79300</v>
+      </c>
+      <c r="E41" s="3">
         <v>152000</v>
       </c>
-      <c r="E41" s="3">
-        <v>2141400</v>
-      </c>
-      <c r="F41" s="3">
-        <v>2359600</v>
-      </c>
-      <c r="G41" s="3">
-        <v>3214000</v>
+      <c r="F41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H41" s="3">
-        <v>3710900</v>
-      </c>
-      <c r="I41" s="3">
-        <v>3523600</v>
+        <v>325400</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J41" s="3">
+        <v>466000</v>
+      </c>
+      <c r="K41" s="3">
         <v>4342000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>657500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>408700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>221800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>163400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>178800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>200200</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2546,52 +2633,55 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>105100</v>
+      </c>
+      <c r="E42" s="3">
         <v>55500</v>
       </c>
-      <c r="E42" s="3">
-        <v>143200</v>
-      </c>
       <c r="F42" s="3">
-        <v>585900</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>235400</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>211200</v>
+        <v>80800</v>
       </c>
       <c r="I42" s="3">
-        <v>753200</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>34800</v>
+      </c>
+      <c r="K42" s="3">
         <v>422300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>3900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>7700</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
+      <c r="Q42" s="3">
+        <v>0</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
@@ -2608,8 +2698,11 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2622,39 +2715,39 @@
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>291600</v>
-      </c>
-      <c r="I43" s="3">
-        <v>286900</v>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J43" s="3">
+        <v>4800</v>
+      </c>
+      <c r="K43" s="3">
         <v>242900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>49400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10700</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N43" s="3">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3">
         <v>4200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>12300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>18400</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2670,8 +2763,11 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2684,14 +2780,14 @@
       <c r="F44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>27200</v>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
@@ -2711,8 +2807,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -2732,53 +2828,56 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>23000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>52000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>129300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>177000</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H45" s="3">
-        <v>101000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>190800</v>
+        <v>14100</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J45" s="3">
+        <v>4800</v>
+      </c>
+      <c r="K45" s="3">
         <v>208500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>27000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>19700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>18600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>23300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>17800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>34500</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2794,53 +2893,56 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>188200</v>
+      </c>
+      <c r="E46" s="3">
         <v>230500</v>
       </c>
-      <c r="E46" s="3">
-        <v>2336700</v>
-      </c>
-      <c r="F46" s="3">
-        <v>3074800</v>
-      </c>
-      <c r="G46" s="3">
-        <v>3626500</v>
+      <c r="F46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H46" s="3">
-        <v>4314700</v>
-      </c>
-      <c r="I46" s="3">
-        <v>4781700</v>
+        <v>424000</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J46" s="3">
+        <v>525800</v>
+      </c>
+      <c r="K46" s="3">
         <v>5215700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>738300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>443000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>240700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>195500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>216600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>253100</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2856,41 +2958,44 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E47" s="3">
         <v>19000</v>
       </c>
-      <c r="E47" s="3">
-        <v>12100</v>
-      </c>
-      <c r="F47" s="3">
-        <v>11400</v>
-      </c>
-      <c r="G47" s="3">
-        <v>30900</v>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H47" s="3">
-        <v>217700</v>
-      </c>
-      <c r="I47" s="3">
-        <v>352100</v>
+        <v>1600</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J47" s="3">
+        <v>4500</v>
+      </c>
+      <c r="K47" s="3">
         <v>578000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>91900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>105400</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2903,8 +3008,8 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -2918,53 +3023,56 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E48" s="3">
         <v>3900</v>
       </c>
-      <c r="E48" s="3">
-        <v>82900</v>
-      </c>
-      <c r="F48" s="3">
-        <v>102500</v>
-      </c>
-      <c r="G48" s="3">
-        <v>124000</v>
+      <c r="F48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H48" s="3">
-        <v>162000</v>
-      </c>
-      <c r="I48" s="3">
-        <v>158500</v>
+        <v>14100</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J48" s="3">
+        <v>18000</v>
+      </c>
+      <c r="K48" s="3">
         <v>65500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6200</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2980,53 +3088,56 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>3</v>
+      <c r="D49" s="3">
+        <v>0</v>
       </c>
       <c r="E49" s="3">
-        <v>118100</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3">
-        <v>281100</v>
+        <v>0</v>
       </c>
       <c r="G49" s="3">
-        <v>281500</v>
+        <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>281900</v>
+        <v>38800</v>
       </c>
       <c r="I49" s="3">
-        <v>282200</v>
+        <v>0</v>
       </c>
       <c r="J49" s="3">
+        <v>40800</v>
+      </c>
+      <c r="K49" s="3">
         <v>282600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>39100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>39300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>44300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>44700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>45500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>49100</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3042,8 +3153,11 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,50 +3283,53 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E52" s="3">
         <v>500</v>
       </c>
-      <c r="E52" s="3">
-        <v>63200</v>
-      </c>
-      <c r="F52" s="3">
-        <v>41900</v>
-      </c>
-      <c r="G52" s="3">
-        <v>10900</v>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H52" s="3">
-        <v>15400</v>
-      </c>
-      <c r="I52" s="3">
-        <v>26600</v>
+        <v>5800</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K52" s="3">
         <v>6100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>300</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
       <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
         <v>2600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>900</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3228,8 +3348,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,53 +3413,56 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>232700</v>
+      </c>
+      <c r="E54" s="3">
         <v>253800</v>
       </c>
-      <c r="E54" s="3">
-        <v>2613000</v>
-      </c>
-      <c r="F54" s="3">
-        <v>3511700</v>
-      </c>
-      <c r="G54" s="3">
-        <v>4073700</v>
+      <c r="F54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H54" s="3">
-        <v>4991600</v>
-      </c>
-      <c r="I54" s="3">
-        <v>5601200</v>
+        <v>484200</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J54" s="3">
+        <v>590600</v>
+      </c>
+      <c r="K54" s="3">
         <v>6148000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>875100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>593500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>291200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>249600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>268600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>308500</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3352,8 +3478,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,44 +3530,45 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>11300</v>
-      </c>
-      <c r="E57" s="3">
-        <v>357800</v>
-      </c>
-      <c r="F57" s="3">
-        <v>595200</v>
-      </c>
-      <c r="G57" s="3">
-        <v>706600</v>
-      </c>
-      <c r="H57" s="3">
-        <v>547500</v>
-      </c>
-      <c r="I57" s="3">
-        <v>593300</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K57" s="3">
         <v>536200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>77400</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3">
         <v>34600</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3453,8 +3584,8 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T57" s="3">
-        <v>0</v>
+      <c r="T57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U57" s="3">
         <v>0</v>
@@ -3462,31 +3593,34 @@
       <c r="V57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>800</v>
       </c>
       <c r="E58" s="3">
-        <v>30000</v>
+        <v>700</v>
       </c>
       <c r="F58" s="3">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>19000</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>7900</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>6200</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3498,17 +3632,17 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>7200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>7900</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3524,53 +3658,56 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>2700</v>
+      <c r="D59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E59" s="3">
-        <v>24100</v>
-      </c>
-      <c r="F59" s="3">
-        <v>37900</v>
-      </c>
-      <c r="G59" s="3">
-        <v>32600</v>
+        <v>2000</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H59" s="3">
-        <v>42500</v>
-      </c>
-      <c r="I59" s="3">
-        <v>30700</v>
+        <v>1500</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J59" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K59" s="3">
         <v>14500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>48200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>77300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>61400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>57300</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3586,53 +3723,56 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E60" s="3">
         <v>14000</v>
       </c>
-      <c r="E60" s="3">
-        <v>411800</v>
-      </c>
-      <c r="F60" s="3">
-        <v>663100</v>
-      </c>
-      <c r="G60" s="3">
-        <v>758200</v>
+      <c r="F60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H60" s="3">
-        <v>590000</v>
-      </c>
-      <c r="I60" s="3">
-        <v>624000</v>
+        <v>91400</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J60" s="3">
+        <v>109900</v>
+      </c>
+      <c r="K60" s="3">
         <v>550600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>79600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>48200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>35700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>84500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>68700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>65200</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3648,16 +3788,19 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -3666,35 +3809,35 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>8900</v>
-      </c>
-      <c r="M61" s="3">
-        <v>9800</v>
       </c>
       <c r="N61" s="3">
         <v>9800</v>
       </c>
       <c r="O61" s="3">
+        <v>9800</v>
+      </c>
+      <c r="P61" s="3">
         <v>10300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>10600</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3710,53 +3853,56 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>3200</v>
-      </c>
-      <c r="E62" s="3">
-        <v>483000</v>
-      </c>
-      <c r="F62" s="3">
-        <v>401800</v>
-      </c>
-      <c r="G62" s="3">
-        <v>405600</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H62" s="3">
-        <v>385500</v>
-      </c>
-      <c r="I62" s="3">
-        <v>417600</v>
+        <v>15700</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J62" s="3">
+        <v>15300</v>
+      </c>
+      <c r="K62" s="3">
         <v>137700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>18000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>19600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1600</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3772,8 +3918,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,53 +4113,56 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E66" s="3">
         <v>17200</v>
       </c>
-      <c r="E66" s="3">
-        <v>894800</v>
-      </c>
-      <c r="F66" s="3">
-        <v>1064900</v>
-      </c>
-      <c r="G66" s="3">
-        <v>1163800</v>
+      <c r="F66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H66" s="3">
-        <v>975500</v>
-      </c>
-      <c r="I66" s="3">
-        <v>1041600</v>
+        <v>146800</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J66" s="3">
+        <v>168700</v>
+      </c>
+      <c r="K66" s="3">
         <v>688300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>97600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>76800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>49000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>96000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>80300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>77500</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4020,8 +4178,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4204,17 +4372,17 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
         <v>445800</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>425700</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>459900</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
@@ -4230,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,53 +4463,56 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1277000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1256500</v>
       </c>
-      <c r="E72" s="3">
-        <v>-8327800</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-7634900</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-6862200</v>
+      <c r="F72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H72" s="3">
-        <v>-5401700</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-4354800</v>
+        <v>-1052800</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J72" s="3">
+        <v>-994900</v>
+      </c>
+      <c r="K72" s="3">
         <v>-3099800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-279500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-423200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-437400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-358200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-309300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-295300</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4354,8 +4528,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,53 +4723,56 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>217900</v>
+      </c>
+      <c r="E76" s="3">
         <v>236600</v>
       </c>
-      <c r="E76" s="3">
-        <v>1718200</v>
-      </c>
-      <c r="F76" s="3">
-        <v>2446800</v>
-      </c>
-      <c r="G76" s="3">
-        <v>2909900</v>
+      <c r="F76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H76" s="3">
-        <v>4016100</v>
+        <v>337400</v>
       </c>
       <c r="I76" s="3">
-        <v>4559600</v>
+        <v>437900</v>
       </c>
       <c r="J76" s="3">
+        <v>421900</v>
+      </c>
+      <c r="K76" s="3">
         <v>5459700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>777400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>516600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>242200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-292200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-237300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-228900</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4602,8 +4788,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
-        <v>45291</v>
-      </c>
       <c r="F80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I80" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44377</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44196</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44104</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44012</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43830</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43738</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43646</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43465</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43373</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43281</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>25100</v>
+        <v>-20500</v>
       </c>
       <c r="E81" s="3">
-        <v>-692900</v>
+        <v>24800</v>
       </c>
       <c r="F81" s="3">
-        <v>-772800</v>
+        <v>2900</v>
       </c>
       <c r="G81" s="3">
-        <v>-1460500</v>
+        <v>-33300</v>
       </c>
       <c r="H81" s="3">
-        <v>-1046900</v>
+        <v>-53300</v>
       </c>
       <c r="I81" s="3">
-        <v>-1255100</v>
+        <v>-56300</v>
       </c>
       <c r="J81" s="3">
+        <v>-105900</v>
+      </c>
+      <c r="K81" s="3">
         <v>-1076500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>145600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-82900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-213300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-35900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-135300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-62000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-17200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-25500</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,8 +5015,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4834,39 +5033,39 @@
       <c r="G83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="H83" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I83" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3">
         <v>2000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1100</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3">
         <v>1400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1000</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4879,8 +5078,11 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,8 +5403,11 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5215,30 +5432,30 @@
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3">
         <v>59900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-80400</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3">
         <v>-124700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-95200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-61400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-43200</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5251,8 +5468,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,31 +5495,32 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -5311,20 +5532,20 @@
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-1800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2200</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5337,8 +5558,11 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,8 +5688,11 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5487,30 +5717,30 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3">
         <v>-27900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-35400</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3">
         <v>30500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>19700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>24900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>1500</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5523,8 +5753,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,31 +5780,32 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5609,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,8 +6038,11 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5821,30 +6067,30 @@
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
         <v>475300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>358400</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3">
         <v>21900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>5800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>227800</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5857,8 +6103,11 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5874,39 +6123,39 @@
       <c r="G101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="H101" s="3">
+        <v>16700</v>
+      </c>
+      <c r="I101" s="3">
+        <v>17600</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
         <v>-14700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1400</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3">
         <v>2200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>11300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>9200</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5919,56 +6168,59 @@
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K102" s="3">
+      <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3">
         <v>492600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>244000</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3">
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3">
         <v>-70000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-58400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-41700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>195300</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5979,6 +6231,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IMAB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IMAB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="92">
   <si>
     <t>IMAB</t>
   </si>
@@ -665,10 +665,9 @@
     <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -704,16 +703,16 @@
         <v>45382</v>
       </c>
       <c r="G7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44926</v>
       </c>
       <c r="K7" s="2">
         <v>44377</v>
@@ -769,16 +768,16 @@
         <v>3</v>
       </c>
       <c r="G8" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="H8" s="3">
-        <v>1400</v>
+        <v>500</v>
       </c>
       <c r="I8" s="3">
         <v>1400</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
+      <c r="J8" s="3">
+        <v>1400</v>
       </c>
       <c r="K8" s="3">
         <v>17800</v>
@@ -842,8 +841,8 @@
       <c r="I9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J9" s="3">
-        <v>0</v>
+      <c r="J9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -899,16 +898,16 @@
         <v>3</v>
       </c>
       <c r="G10" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="H10" s="3">
-        <v>1400</v>
+        <v>500</v>
       </c>
       <c r="I10" s="3">
         <v>1400</v>
       </c>
       <c r="J10" s="3">
-        <v>-19800</v>
+        <v>1400</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -989,16 +988,16 @@
         <v>5400</v>
       </c>
       <c r="G12" s="3">
-        <v>5100</v>
+        <v>25700</v>
       </c>
       <c r="H12" s="3">
+        <v>25000</v>
+      </c>
+      <c r="I12" s="3">
         <v>30800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>32500</v>
-      </c>
-      <c r="J12" s="3">
-        <v>32800</v>
       </c>
       <c r="K12" s="3">
         <v>593000</v>
@@ -1118,17 +1117,17 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3">
+        <v>10200</v>
+      </c>
+      <c r="H14" s="3">
+        <v>9900</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
-        <v>1000</v>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -1184,16 +1183,16 @@
         <v>800</v>
       </c>
       <c r="G15" s="3">
+        <v>800</v>
+      </c>
+      <c r="H15" s="3">
         <v>900</v>
       </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
       <c r="I15" s="3">
         <v>0</v>
       </c>
       <c r="J15" s="3">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1271,16 +1270,16 @@
         <v>12600</v>
       </c>
       <c r="G17" s="3">
-        <v>10900</v>
+        <v>40400</v>
       </c>
       <c r="H17" s="3">
+        <v>39200</v>
+      </c>
+      <c r="I17" s="3">
         <v>47700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>50300</v>
-      </c>
-      <c r="J17" s="3">
-        <v>63500</v>
       </c>
       <c r="K17" s="3">
         <v>1044500</v>
@@ -1336,16 +1335,16 @@
         <v>-12600</v>
       </c>
       <c r="G18" s="3">
-        <v>-10600</v>
+        <v>-39800</v>
       </c>
       <c r="H18" s="3">
+        <v>-38700</v>
+      </c>
+      <c r="I18" s="3">
         <v>-46300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-48900</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-83300</v>
       </c>
       <c r="K18" s="3">
         <v>-1026700</v>
@@ -1426,16 +1425,16 @@
         <v>-1400</v>
       </c>
       <c r="G20" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="H20" s="3">
+        <v>400</v>
+      </c>
+      <c r="I20" s="3">
         <v>9100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>9600</v>
-      </c>
-      <c r="J20" s="3">
-        <v>23000</v>
       </c>
       <c r="K20" s="3">
         <v>-52900</v>
@@ -1491,16 +1490,16 @@
         <v>-10300</v>
       </c>
       <c r="G21" s="3">
-        <v>-9800</v>
+        <v>-39300</v>
       </c>
       <c r="H21" s="3">
+        <v>-38200</v>
+      </c>
+      <c r="I21" s="3">
         <v>-55400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-58500</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-105400</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1555,8 +1554,8 @@
       <c r="F22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
+      <c r="G22" s="3">
+        <v>0</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
@@ -1621,16 +1620,16 @@
         <v>-9700</v>
       </c>
       <c r="G23" s="3">
-        <v>-8200</v>
+        <v>-48900</v>
       </c>
       <c r="H23" s="3">
+        <v>-47500</v>
+      </c>
+      <c r="I23" s="3">
         <v>-53300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-56300</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-105800</v>
       </c>
       <c r="K23" s="3">
         <v>-1079600</v>
@@ -1694,8 +1693,8 @@
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J24" s="3">
-        <v>100</v>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>-3100</v>
@@ -1816,16 +1815,16 @@
         <v>-9700</v>
       </c>
       <c r="G26" s="3">
-        <v>-8200</v>
+        <v>-48900</v>
       </c>
       <c r="H26" s="3">
+        <v>-47500</v>
+      </c>
+      <c r="I26" s="3">
         <v>-53300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-56300</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-105900</v>
       </c>
       <c r="K26" s="3">
         <v>-1076500</v>
@@ -1881,16 +1880,16 @@
         <v>2900</v>
       </c>
       <c r="G27" s="3">
-        <v>-33300</v>
+        <v>-48900</v>
       </c>
       <c r="H27" s="3">
+        <v>-47500</v>
+      </c>
+      <c r="I27" s="3">
         <v>-53300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-56300</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-105900</v>
       </c>
       <c r="K27" s="3">
         <v>-1076500</v>
@@ -2011,7 +2010,7 @@
         <v>12600</v>
       </c>
       <c r="G29" s="3">
-        <v>-25000</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
@@ -2206,16 +2205,16 @@
         <v>1400</v>
       </c>
       <c r="G32" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="H32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I32" s="3">
         <v>-9100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-9600</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-23000</v>
       </c>
       <c r="K32" s="3">
         <v>52900</v>
@@ -2271,16 +2270,16 @@
         <v>2900</v>
       </c>
       <c r="G33" s="3">
-        <v>-33300</v>
+        <v>-48900</v>
       </c>
       <c r="H33" s="3">
+        <v>-47500</v>
+      </c>
+      <c r="I33" s="3">
         <v>-53300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-56300</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-105900</v>
       </c>
       <c r="K33" s="3">
         <v>-1076500</v>
@@ -2401,16 +2400,16 @@
         <v>2900</v>
       </c>
       <c r="G35" s="3">
-        <v>-33300</v>
+        <v>-48900</v>
       </c>
       <c r="H35" s="3">
+        <v>-47500</v>
+      </c>
+      <c r="I35" s="3">
         <v>-53300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-56300</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-105900</v>
       </c>
       <c r="K35" s="3">
         <v>-1076500</v>
@@ -2471,16 +2470,16 @@
         <v>45382</v>
       </c>
       <c r="G38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44926</v>
       </c>
       <c r="K38" s="2">
         <v>44377</v>
@@ -2576,8 +2575,8 @@
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
-        <v>79300</v>
+      <c r="D41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E41" s="3">
         <v>152000</v>
@@ -2585,17 +2584,17 @@
       <c r="F41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
+      <c r="G41" s="3">
+        <v>302000</v>
       </c>
       <c r="H41" s="3">
+        <v>293500</v>
+      </c>
+      <c r="I41" s="3">
         <v>325400</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3">
-        <v>466000</v>
+      <c r="J41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K41" s="3">
         <v>4342000</v>
@@ -2642,7 +2641,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>105100</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
         <v>55500</v>
@@ -2651,16 +2650,16 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>20900</v>
       </c>
       <c r="H42" s="3">
+        <v>20300</v>
+      </c>
+      <c r="I42" s="3">
         <v>80800</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
-        <v>34800</v>
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>422300</v>
@@ -2715,17 +2714,17 @@
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
+      <c r="G43" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H43" s="3">
+        <v>2500</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J43" s="3">
-        <v>4800</v>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>242900</v>
@@ -2845,17 +2844,17 @@
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
+      <c r="G45" s="3">
+        <v>1300</v>
       </c>
       <c r="H45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I45" s="3">
         <v>14100</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3">
-        <v>4800</v>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K45" s="3">
         <v>208500</v>
@@ -2901,8 +2900,8 @@
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
-        <v>188200</v>
+      <c r="D46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E46" s="3">
         <v>230500</v>
@@ -2910,17 +2909,17 @@
       <c r="F46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
+      <c r="G46" s="3">
+        <v>329500</v>
       </c>
       <c r="H46" s="3">
+        <v>320200</v>
+      </c>
+      <c r="I46" s="3">
         <v>424000</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3">
-        <v>525800</v>
+      <c r="J46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K46" s="3">
         <v>5215700</v>
@@ -2966,8 +2965,8 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>39300</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E47" s="3">
         <v>19000</v>
@@ -2975,17 +2974,17 @@
       <c r="F47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
+      <c r="G47" s="3">
+        <v>1700</v>
       </c>
       <c r="H47" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I47" s="3">
         <v>1600</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3">
-        <v>4500</v>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>578000</v>
@@ -3031,8 +3030,8 @@
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>3700</v>
+      <c r="D48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E48" s="3">
         <v>3900</v>
@@ -3040,17 +3039,17 @@
       <c r="F48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
+      <c r="G48" s="3">
+        <v>11700</v>
       </c>
       <c r="H48" s="3">
+        <v>11400</v>
+      </c>
+      <c r="I48" s="3">
         <v>14100</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3">
-        <v>18000</v>
+      <c r="J48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K48" s="3">
         <v>65500</v>
@@ -3106,16 +3105,16 @@
         <v>0</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
+        <v>16700</v>
       </c>
       <c r="H49" s="3">
+        <v>16200</v>
+      </c>
+      <c r="I49" s="3">
         <v>38800</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
-        <v>40800</v>
+        <v>0</v>
       </c>
       <c r="K49" s="3">
         <v>282600</v>
@@ -3291,8 +3290,8 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>1400</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E52" s="3">
         <v>500</v>
@@ -3300,17 +3299,17 @@
       <c r="F52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
+      <c r="G52" s="3">
+        <v>8900</v>
       </c>
       <c r="H52" s="3">
+        <v>8700</v>
+      </c>
+      <c r="I52" s="3">
         <v>5800</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3">
-        <v>1600</v>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>6100</v>
@@ -3421,8 +3420,8 @@
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
-        <v>232700</v>
+      <c r="D54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E54" s="3">
         <v>253800</v>
@@ -3430,17 +3429,17 @@
       <c r="F54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
+      <c r="G54" s="3">
+        <v>368500</v>
       </c>
       <c r="H54" s="3">
+        <v>358100</v>
+      </c>
+      <c r="I54" s="3">
         <v>484200</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3">
-        <v>590600</v>
+      <c r="J54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K54" s="3">
         <v>6148000</v>
@@ -3602,7 +3601,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="E58" s="3">
         <v>700</v>
@@ -3611,16 +3610,16 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>7300</v>
       </c>
       <c r="H58" s="3">
+        <v>7100</v>
+      </c>
+      <c r="I58" s="3">
         <v>7900</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
-        <v>6200</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3675,17 +3674,17 @@
       <c r="F59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
+      <c r="G59" s="3">
+        <v>1800</v>
       </c>
       <c r="H59" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I59" s="3">
         <v>1500</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3">
-        <v>3200</v>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K59" s="3">
         <v>14500</v>
@@ -3731,8 +3730,8 @@
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>11800</v>
+      <c r="D60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E60" s="3">
         <v>14000</v>
@@ -3740,17 +3739,17 @@
       <c r="F60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
+      <c r="G60" s="3">
+        <v>58100</v>
       </c>
       <c r="H60" s="3">
+        <v>56400</v>
+      </c>
+      <c r="I60" s="3">
         <v>91400</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3">
-        <v>109900</v>
+      <c r="J60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K60" s="3">
         <v>550600</v>
@@ -3797,7 +3796,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
         <v>3200</v>
@@ -3806,16 +3805,16 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="H61" s="3">
+        <v>3200</v>
+      </c>
+      <c r="I61" s="3">
         <v>2800</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
-        <v>4600</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3870,17 +3869,17 @@
       <c r="F62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
+      <c r="G62" s="3">
+        <v>23700</v>
       </c>
       <c r="H62" s="3">
+        <v>23000</v>
+      </c>
+      <c r="I62" s="3">
         <v>15700</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3">
-        <v>15300</v>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3">
         <v>137700</v>
@@ -4121,8 +4120,8 @@
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
-        <v>14800</v>
+      <c r="D66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E66" s="3">
         <v>17200</v>
@@ -4130,17 +4129,17 @@
       <c r="F66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
+      <c r="G66" s="3">
+        <v>126200</v>
       </c>
       <c r="H66" s="3">
+        <v>122600</v>
+      </c>
+      <c r="I66" s="3">
         <v>146800</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3">
-        <v>168700</v>
+      <c r="J66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K66" s="3">
         <v>688300</v>
@@ -4471,8 +4470,8 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>-1277000</v>
+      <c r="D72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E72" s="3">
         <v>-1256500</v>
@@ -4480,17 +4479,17 @@
       <c r="F72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
+      <c r="G72" s="3">
+        <v>-1174400</v>
       </c>
       <c r="H72" s="3">
+        <v>-1141300</v>
+      </c>
+      <c r="I72" s="3">
         <v>-1052800</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-994900</v>
+      <c r="J72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K72" s="3">
         <v>-3099800</v>
@@ -4732,7 +4731,7 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>217900</v>
+        <v>236600</v>
       </c>
       <c r="E76" s="3">
         <v>236600</v>
@@ -4740,17 +4739,17 @@
       <c r="F76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
+      <c r="G76" s="3">
+        <v>242300</v>
       </c>
       <c r="H76" s="3">
+        <v>235500</v>
+      </c>
+      <c r="I76" s="3">
         <v>337400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>437900</v>
-      </c>
-      <c r="J76" s="3">
-        <v>421900</v>
       </c>
       <c r="K76" s="3">
         <v>5459700</v>
@@ -4876,16 +4875,16 @@
         <v>45382</v>
       </c>
       <c r="G80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44926</v>
       </c>
       <c r="K80" s="2">
         <v>44377</v>
@@ -4941,16 +4940,16 @@
         <v>2900</v>
       </c>
       <c r="G81" s="3">
-        <v>-33300</v>
+        <v>-48900</v>
       </c>
       <c r="H81" s="3">
+        <v>-47500</v>
+      </c>
+      <c r="I81" s="3">
         <v>-53300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-56300</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-105900</v>
       </c>
       <c r="K81" s="3">
         <v>-1076500</v>
@@ -5033,14 +5032,14 @@
       <c r="G83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3">
         <v>2500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2600</v>
-      </c>
-      <c r="J83" s="3">
-        <v>1400</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -6123,14 +6122,14 @@
       <c r="G101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3">
         <v>16700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>17600</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-4600</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Quarterly/IMAB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IMAB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="92">
   <si>
     <t>IMAB</t>
   </si>
@@ -656,105 +656,112 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44196</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44104</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44012</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43830</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43738</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43646</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43465</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43373</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43281</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -767,59 +774,65 @@
       <c r="F8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G8" s="3">
-        <v>600</v>
-      </c>
-      <c r="H8" s="3">
-        <v>500</v>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I8" s="3">
+        <v>200</v>
+      </c>
+      <c r="J8" s="3">
+        <v>200</v>
+      </c>
+      <c r="K8" s="3">
         <v>1400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>17800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>213100</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
       <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
         <v>4300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>2200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>2400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>8300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>3400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>3300</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -883,8 +896,14 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -897,24 +916,24 @@
       <c r="F10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G10" s="3">
-        <v>600</v>
-      </c>
-      <c r="H10" s="3">
-        <v>500</v>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I10" s="3">
+        <v>200</v>
+      </c>
+      <c r="J10" s="3">
+        <v>200</v>
+      </c>
+      <c r="K10" s="3">
         <v>1400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>1400</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -948,8 +967,14 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -973,73 +998,81 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>800</v>
+      </c>
+      <c r="E12" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F12" s="3">
         <v>4500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>3100</v>
       </c>
-      <c r="F12" s="3">
-        <v>5400</v>
-      </c>
-      <c r="G12" s="3">
-        <v>25700</v>
-      </c>
       <c r="H12" s="3">
-        <v>25000</v>
+        <v>6100</v>
       </c>
       <c r="I12" s="3">
+        <v>6200</v>
+      </c>
+      <c r="J12" s="3">
+        <v>6200</v>
+      </c>
+      <c r="K12" s="3">
         <v>30800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>32500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>593000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>74900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>35400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>62900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>120700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>45800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>41800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>65600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>17100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>31000</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1103,31 +1136,37 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="E14" s="3">
+        <v>1200</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>10200</v>
-      </c>
-      <c r="H14" s="3">
-        <v>9900</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
+        <v>11500</v>
+      </c>
+      <c r="J14" s="3">
+        <v>11500</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -1141,15 +1180,15 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>3300</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1162,37 +1201,43 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>100</v>
+      </c>
+      <c r="E15" s="3">
+        <v>100</v>
+      </c>
+      <c r="F15" s="3">
         <v>900</v>
-      </c>
-      <c r="E15" s="3">
-        <v>800</v>
-      </c>
-      <c r="F15" s="3">
-        <v>800</v>
       </c>
       <c r="G15" s="3">
         <v>800</v>
       </c>
       <c r="H15" s="3">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1233,8 +1278,14 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1255,138 +1306,152 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>13400</v>
+      </c>
+      <c r="F17" s="3">
         <v>12400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>15000</v>
       </c>
-      <c r="F17" s="3">
-        <v>12600</v>
-      </c>
-      <c r="G17" s="3">
-        <v>40400</v>
-      </c>
       <c r="H17" s="3">
-        <v>39200</v>
+        <v>8500</v>
       </c>
       <c r="I17" s="3">
+        <v>13300</v>
+      </c>
+      <c r="J17" s="3">
+        <v>13300</v>
+      </c>
+      <c r="K17" s="3">
         <v>47700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>50300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1044500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>106900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>54600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>87200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>218000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>46900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>132500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>75800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>20500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>33800</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-12400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-15000</v>
       </c>
-      <c r="F18" s="3">
-        <v>-12600</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-39800</v>
-      </c>
       <c r="H18" s="3">
-        <v>-38700</v>
+        <v>-8500</v>
       </c>
       <c r="I18" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="K18" s="3">
         <v>-46300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-48900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-1026700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>106300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-54600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-87200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-213700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-44700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-130100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-67500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-17100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-30600</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1410,138 +1475,152 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F20" s="3">
         <v>10500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-5900</v>
       </c>
-      <c r="F20" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I20" s="3">
+        <v>11100</v>
+      </c>
+      <c r="J20" s="3">
+        <v>11100</v>
+      </c>
+      <c r="K20" s="3">
+        <v>9100</v>
+      </c>
+      <c r="L20" s="3">
+        <v>9600</v>
+      </c>
+      <c r="M20" s="3">
+        <v>-52900</v>
+      </c>
+      <c r="N20" s="3">
+        <v>41000</v>
+      </c>
+      <c r="O20" s="3">
+        <v>56300</v>
+      </c>
+      <c r="P20" s="3">
+        <v>4500</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>5600</v>
+      </c>
+      <c r="R20" s="3">
+        <v>8900</v>
+      </c>
+      <c r="S20" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="T20" s="3">
+        <v>7600</v>
+      </c>
+      <c r="U20" s="3">
         <v>400</v>
       </c>
-      <c r="H20" s="3">
-        <v>400</v>
-      </c>
-      <c r="I20" s="3">
-        <v>9100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>9600</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-52900</v>
-      </c>
-      <c r="L20" s="3">
-        <v>41000</v>
-      </c>
-      <c r="M20" s="3">
-        <v>56300</v>
-      </c>
-      <c r="N20" s="3">
-        <v>4500</v>
-      </c>
-      <c r="O20" s="3">
-        <v>5600</v>
-      </c>
-      <c r="P20" s="3">
-        <v>8900</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="R20" s="3">
-        <v>7600</v>
-      </c>
-      <c r="S20" s="3">
-        <v>400</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>6500</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="F21" s="3">
         <v>-22100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-8300</v>
       </c>
-      <c r="F21" s="3">
-        <v>-10300</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-39300</v>
-      </c>
       <c r="H21" s="3">
-        <v>-38200</v>
+        <v>-10000</v>
       </c>
       <c r="I21" s="3">
+        <v>-24100</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-24200</v>
+      </c>
+      <c r="K21" s="3">
         <v>-55400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-58500</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>149300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>2800</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-206700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-34900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-134200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-58900</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3">
         <v>-23900</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1554,17 +1633,17 @@
       <c r="F22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1576,102 +1655,114 @@
         <v>0</v>
       </c>
       <c r="N22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O22" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="P22" s="3">
         <v>100</v>
       </c>
       <c r="Q22" s="3">
+        <v>400</v>
+      </c>
+      <c r="R22" s="3">
+        <v>100</v>
+      </c>
+      <c r="S22" s="3">
         <v>300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>1800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>1400</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="F23" s="3">
         <v>-20500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-7200</v>
       </c>
-      <c r="F23" s="3">
-        <v>-9700</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-48900</v>
-      </c>
       <c r="H23" s="3">
-        <v>-47500</v>
+        <v>-9400</v>
       </c>
       <c r="I23" s="3">
+        <v>-33400</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-33400</v>
+      </c>
+      <c r="K23" s="3">
         <v>-53300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-56300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-1079600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>147300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-82900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-208500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-35900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-135300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-61800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-17000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-25500</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1696,18 +1787,18 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3">
         <v>-3100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>1700</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
@@ -1718,25 +1809,31 @@
         <v>0</v>
       </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
+      <c r="V24" s="3">
+        <v>0</v>
       </c>
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1800,138 +1897,156 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="F26" s="3">
         <v>-20500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-7200</v>
       </c>
-      <c r="F26" s="3">
-        <v>-9700</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-48900</v>
-      </c>
       <c r="H26" s="3">
-        <v>-47500</v>
+        <v>-9400</v>
       </c>
       <c r="I26" s="3">
+        <v>-33400</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-33400</v>
+      </c>
+      <c r="K26" s="3">
         <v>-53300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-56300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-1076500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>145600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>1700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-82900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-208500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-35900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-135300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-62000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-17200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-25500</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-20500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>24800</v>
       </c>
-      <c r="F27" s="3">
-        <v>2900</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-48900</v>
-      </c>
       <c r="H27" s="3">
-        <v>-47500</v>
+        <v>-16300</v>
       </c>
       <c r="I27" s="3">
+        <v>-61800</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-61800</v>
+      </c>
+      <c r="K27" s="3">
         <v>-53300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-56300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-1076500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>145600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-82900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-213300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-35900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-135300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-62000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-17200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-25500</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1995,8 +2110,14 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2004,31 +2125,31 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>31900</v>
       </c>
-      <c r="F29" s="3">
-        <v>12600</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>-6900</v>
       </c>
       <c r="I29" s="3">
-        <v>0</v>
+        <v>-28400</v>
       </c>
       <c r="J29" s="3">
-        <v>0</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
+        <v>-28400</v>
+      </c>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -2060,8 +2181,14 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2125,8 +2252,14 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2190,138 +2323,156 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>200</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F32" s="3">
         <v>-10500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>5900</v>
       </c>
-      <c r="F32" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="M32" s="3">
+        <v>52900</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-56300</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="R32" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="S32" s="3">
+        <v>4800</v>
+      </c>
+      <c r="T32" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="U32" s="3">
         <v>-400</v>
       </c>
-      <c r="H32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-9100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-9600</v>
-      </c>
-      <c r="K32" s="3">
-        <v>52900</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-41000</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-56300</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-8900</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>4800</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-7600</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-6500</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-20500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>24800</v>
       </c>
-      <c r="F33" s="3">
-        <v>2900</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-48900</v>
-      </c>
       <c r="H33" s="3">
-        <v>-47500</v>
+        <v>-16300</v>
       </c>
       <c r="I33" s="3">
+        <v>-61800</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-61800</v>
+      </c>
+      <c r="K33" s="3">
         <v>-53300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-56300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-1076500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>145600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-82900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-213300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-35900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-135300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-62000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-17200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-25500</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2385,143 +2536,161 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-20500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>24800</v>
       </c>
-      <c r="F35" s="3">
-        <v>2900</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-48900</v>
-      </c>
       <c r="H35" s="3">
-        <v>-47500</v>
+        <v>-16300</v>
       </c>
       <c r="I35" s="3">
+        <v>-61800</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-61800</v>
+      </c>
+      <c r="K35" s="3">
         <v>-53300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-56300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-1076500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>145600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-82900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-213300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-35900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-135300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-62000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-17200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-25500</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44196</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44104</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44012</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43830</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43738</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43646</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43465</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43373</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43281</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2545,8 +2714,10 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2570,59 +2741,61 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>3</v>
+      <c r="D41" s="3">
+        <v>53600</v>
       </c>
       <c r="E41" s="3">
+        <v>68300</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G41" s="3">
         <v>152000</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G41" s="3">
-        <v>302000</v>
-      </c>
-      <c r="H41" s="3">
-        <v>293500</v>
+      <c r="H41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I41" s="3">
+        <v>291500</v>
+      </c>
+      <c r="J41" s="3">
+        <v>291500</v>
+      </c>
+      <c r="K41" s="3">
         <v>325400</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3">
         <v>4342000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>657500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>408700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>221800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>163400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>178800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>200200</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2635,58 +2808,64 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>115000</v>
       </c>
       <c r="E42" s="3">
+        <v>105100</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>55500</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>20900</v>
-      </c>
       <c r="H42" s="3">
-        <v>20300</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>20200</v>
+      </c>
+      <c r="J42" s="3">
+        <v>20200</v>
+      </c>
+      <c r="K42" s="3">
         <v>80800</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>422300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>4400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>3900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>4600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>7700</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
+      <c r="S42" s="3">
+        <v>0</v>
       </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
@@ -2700,59 +2879,65 @@
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
+      <c r="E43" s="3">
+        <v>1200</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G43" s="3">
-        <v>2500</v>
-      </c>
-      <c r="H43" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J43" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3">
         <v>242900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>49400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>10700</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3">
         <v>4200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>12300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>18400</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2765,8 +2950,14 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2809,11 +3000,11 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
-      <c r="R44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
@@ -2830,59 +3021,65 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1000</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>1200</v>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I45" s="3">
+        <v>16200</v>
+      </c>
+      <c r="J45" s="3">
+        <v>16200</v>
+      </c>
+      <c r="K45" s="3">
         <v>14100</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>208500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>27000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>19700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>18600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>23300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>17800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>34500</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2895,59 +3092,65 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>3</v>
+      <c r="D46" s="3">
+        <v>173200</v>
       </c>
       <c r="E46" s="3">
+        <v>176700</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G46" s="3">
         <v>230500</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G46" s="3">
-        <v>329500</v>
-      </c>
-      <c r="H46" s="3">
-        <v>320200</v>
+      <c r="H46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I46" s="3">
+        <v>329900</v>
+      </c>
+      <c r="J46" s="3">
+        <v>329900</v>
+      </c>
+      <c r="K46" s="3">
         <v>424000</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3">
         <v>5215700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>738300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>443000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>240700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>195500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>216600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>253100</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2960,47 +3163,53 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>3</v>
+      <c r="D47" s="3">
+        <v>30800</v>
       </c>
       <c r="E47" s="3">
+        <v>30800</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3">
         <v>19000</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G47" s="3">
-        <v>1700</v>
-      </c>
-      <c r="H47" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
         <v>1600</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
         <v>578000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>91900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>105400</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3010,11 +3219,11 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
-      </c>
-      <c r="T47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U47" s="3">
         <v>0</v>
@@ -3025,59 +3234,65 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>3</v>
+      <c r="D48" s="3">
+        <v>3600</v>
       </c>
       <c r="E48" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="3">
         <v>3900</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G48" s="3">
-        <v>11700</v>
-      </c>
-      <c r="H48" s="3">
-        <v>11400</v>
+      <c r="H48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I48" s="3">
+        <v>5600</v>
+      </c>
+      <c r="J48" s="3">
+        <v>5600</v>
+      </c>
+      <c r="K48" s="3">
         <v>14100</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3">
         <v>65500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>5600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>5800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>6300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>6700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>5600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>6200</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3090,8 +3305,14 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3105,44 +3326,44 @@
         <v>0</v>
       </c>
       <c r="G49" s="3">
-        <v>16700</v>
+        <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>16200</v>
+        <v>0</v>
       </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>38800</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>282600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>39100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>39300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>44300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>44700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>45500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>49100</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3155,8 +3376,14 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3220,8 +3447,14 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3285,56 +3518,62 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>1300</v>
       </c>
       <c r="E52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3">
         <v>500</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G52" s="3">
-        <v>8900</v>
-      </c>
-      <c r="H52" s="3">
-        <v>8700</v>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I52" s="3">
+        <v>33500</v>
+      </c>
+      <c r="J52" s="3">
+        <v>33500</v>
+      </c>
+      <c r="K52" s="3">
         <v>5800</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3">
         <v>6100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>300</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
-      <c r="N52" s="3">
-        <v>0</v>
-      </c>
       <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
         <v>2600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>900</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,8 +3589,14 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3415,59 +3660,65 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>3</v>
+      <c r="D54" s="3">
+        <v>208900</v>
       </c>
       <c r="E54" s="3">
+        <v>212700</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G54" s="3">
         <v>253800</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G54" s="3">
-        <v>368500</v>
-      </c>
-      <c r="H54" s="3">
-        <v>358100</v>
+      <c r="H54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I54" s="3">
+        <v>368900</v>
+      </c>
+      <c r="J54" s="3">
+        <v>368900</v>
+      </c>
+      <c r="K54" s="3">
         <v>484200</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3">
         <v>6148000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>875100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>593500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>291200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>249600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>268600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>308500</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3480,8 +3731,14 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3505,8 +3762,10 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3530,8 +3789,10 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3556,24 +3817,24 @@
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3">
         <v>536200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>77400</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3">
         <v>34600</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3586,68 +3847,74 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
-      </c>
-      <c r="V57" s="3">
-        <v>0</v>
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E58" s="3">
+        <v>800</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>700</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>600</v>
+      </c>
+      <c r="J58" s="3">
+        <v>600</v>
+      </c>
+      <c r="K58" s="3">
+        <v>7900</v>
+      </c>
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>7200</v>
+      </c>
+      <c r="R58" s="3">
         <v>7300</v>
       </c>
-      <c r="H58" s="3">
-        <v>7100</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="S58" s="3">
         <v>7900</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3">
-        <v>7200</v>
-      </c>
-      <c r="P58" s="3">
-        <v>7300</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>7900</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3660,8 +3927,14 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3669,50 +3942,50 @@
         <v>3</v>
       </c>
       <c r="E59" s="3">
+        <v>100</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3">
         <v>2000</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1800</v>
-      </c>
-      <c r="H59" s="3">
-        <v>1700</v>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I59" s="3">
+        <v>50900</v>
+      </c>
+      <c r="J59" s="3">
+        <v>50900</v>
+      </c>
+      <c r="K59" s="3">
         <v>1500</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>14500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>48200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>77300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>61400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>57300</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3725,59 +3998,65 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>3</v>
+      <c r="D60" s="3">
+        <v>7800</v>
       </c>
       <c r="E60" s="3">
+        <v>8500</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G60" s="3">
         <v>14000</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I60" s="3">
         <v>58100</v>
       </c>
-      <c r="H60" s="3">
-        <v>56400</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
+        <v>58100</v>
+      </c>
+      <c r="K60" s="3">
         <v>91400</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3">
         <v>550600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>79600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>48200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>35700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>84500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>68700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>65200</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3790,59 +4069,65 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="E61" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>3200</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>3300</v>
       </c>
-      <c r="H61" s="3">
-        <v>3200</v>
-      </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K61" s="3">
         <v>2800</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>8900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>9800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>9800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>10300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>10600</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -3855,8 +4140,14 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3869,44 +4160,44 @@
       <c r="F62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G62" s="3">
-        <v>23700</v>
-      </c>
-      <c r="H62" s="3">
-        <v>23000</v>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I62" s="3">
+        <v>64900</v>
+      </c>
+      <c r="J62" s="3">
+        <v>64900</v>
+      </c>
+      <c r="K62" s="3">
         <v>15700</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>137700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>18000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>19600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>3500</v>
-      </c>
-      <c r="O62" s="3">
-        <v>1600</v>
-      </c>
-      <c r="P62" s="3">
-        <v>1300</v>
       </c>
       <c r="Q62" s="3">
         <v>1600</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
+      <c r="R62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="S62" s="3">
+        <v>1600</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
@@ -3920,8 +4211,14 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3985,8 +4282,14 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4050,8 +4353,14 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4115,59 +4424,65 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>3</v>
+      <c r="D66" s="3">
+        <v>10600</v>
       </c>
       <c r="E66" s="3">
+        <v>11500</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G66" s="3">
         <v>17200</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G66" s="3">
-        <v>126200</v>
-      </c>
-      <c r="H66" s="3">
-        <v>122600</v>
+      <c r="H66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I66" s="3">
+        <v>126300</v>
+      </c>
+      <c r="J66" s="3">
+        <v>126300</v>
+      </c>
+      <c r="K66" s="3">
         <v>146800</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3">
         <v>688300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>97600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>76800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>49000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>96000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>80300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>77500</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4180,8 +4495,14 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4205,8 +4526,10 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4270,8 +4593,14 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4335,8 +4664,14 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4374,20 +4709,20 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>445800</v>
       </c>
-      <c r="P70" s="3">
+      <c r="R70" s="3">
         <v>425700</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="S70" s="3">
         <v>459900</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -4400,8 +4735,14 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4465,59 +4806,65 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>3</v>
+      <c r="D72" s="3">
+        <v>-1289200</v>
       </c>
       <c r="E72" s="3">
+        <v>-1286000</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G72" s="3">
         <v>-1256500</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-1174400</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-1141300</v>
+      <c r="H72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I72" s="3">
+        <v>-1263800</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-1263800</v>
+      </c>
+      <c r="K72" s="3">
         <v>-1052800</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3">
         <v>-3099800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-279500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-423200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-437400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-358200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-309300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-295300</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4530,8 +4877,14 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4595,8 +4948,14 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4660,8 +5019,14 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4725,59 +5090,65 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>198300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>201200</v>
+      </c>
+      <c r="F76" s="3">
         <v>236600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>236600</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G76" s="3">
-        <v>242300</v>
-      </c>
       <c r="H76" s="3">
-        <v>235500</v>
+        <v>242600</v>
       </c>
       <c r="I76" s="3">
+        <v>242600</v>
+      </c>
+      <c r="J76" s="3">
+        <v>242600</v>
+      </c>
+      <c r="K76" s="3">
         <v>337400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>437900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>5459700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>777400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>516600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>242200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-292200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-237300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-228900</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,8 +5161,14 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4855,143 +5232,161 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44196</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44104</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44012</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43830</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43738</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43646</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43465</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43373</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43281</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-20500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>24800</v>
       </c>
-      <c r="F81" s="3">
-        <v>2900</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-48900</v>
-      </c>
       <c r="H81" s="3">
-        <v>-47500</v>
+        <v>-16300</v>
       </c>
       <c r="I81" s="3">
+        <v>-61800</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-61800</v>
+      </c>
+      <c r="K81" s="3">
         <v>-53300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-56300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-1076500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>145600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-82900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-213300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-35900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-135300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-62000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-17200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-25500</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5015,8 +5410,10 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5035,41 +5432,41 @@
       <c r="H83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K83" s="3">
         <v>2500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>2600</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3">
         <v>2000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>1100</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3">
         <v>1400</v>
-      </c>
-      <c r="P83" s="3">
-        <v>1000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>700</v>
       </c>
       <c r="R83" s="3">
         <v>1000</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
+      <c r="S83" s="3">
+        <v>700</v>
+      </c>
+      <c r="T83" s="3">
+        <v>1000</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
@@ -5080,8 +5477,14 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5145,8 +5548,14 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5210,8 +5619,14 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5275,8 +5690,14 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5340,8 +5761,14 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5405,8 +5832,14 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5434,33 +5867,33 @@
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3">
         <v>59900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-80400</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-124700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-95200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-61400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-43200</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5470,8 +5903,14 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5495,8 +5934,10 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5521,11 +5962,11 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -5534,23 +5975,23 @@
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-1800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-2200</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5560,8 +6001,14 @@
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5625,8 +6072,14 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5690,8 +6143,14 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5719,33 +6178,33 @@
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3">
         <v>-27900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-35400</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3">
         <v>30500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>19700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>24900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>1500</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5755,8 +6214,14 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5780,8 +6245,10 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5806,11 +6273,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5845,8 +6312,14 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5910,8 +6383,14 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5975,8 +6454,14 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6040,8 +6525,14 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6069,33 +6560,33 @@
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
         <v>475300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>358400</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3">
         <v>21900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>5800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-4700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>227800</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6105,8 +6596,14 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6125,42 +6622,42 @@
       <c r="H101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I101" s="3">
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K101" s="3">
         <v>16700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>17600</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3">
         <v>-14700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>1400</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3">
         <v>2200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>11300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>9200</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6170,8 +6667,14 @@
       <c r="W101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6196,36 +6699,36 @@
       <c r="J102" s="3">
         <v>0</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
+      <c r="K102" s="3">
+        <v>0</v>
       </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3">
         <v>492600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>244000</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-70000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-58400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-41700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>195300</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6233,6 +6736,12 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IMAB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IMAB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="92">
   <si>
     <t>IMAB</t>
   </si>
@@ -656,112 +656,116 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43830</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43738</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43646</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43465</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43373</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43281</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -780,59 +784,62 @@
       <c r="H8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I8" s="3">
-        <v>200</v>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J8" s="3">
         <v>200</v>
       </c>
       <c r="K8" s="3">
-        <v>1400</v>
+        <v>200</v>
       </c>
       <c r="L8" s="3">
         <v>1400</v>
       </c>
       <c r="M8" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N8" s="3">
         <v>17800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>213100</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
       <c r="P8" s="3">
         <v>0</v>
       </c>
       <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
         <v>4300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3300</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -902,8 +909,11 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -922,20 +932,20 @@
       <c r="H10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I10" s="3">
-        <v>200</v>
+      <c r="I10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J10" s="3">
         <v>200</v>
       </c>
       <c r="K10" s="3">
-        <v>1400</v>
+        <v>200</v>
       </c>
       <c r="L10" s="3">
         <v>1400</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
+      <c r="M10" s="3">
+        <v>1400</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
@@ -973,8 +983,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1000,79 +1013,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
-        <v>800</v>
-      </c>
-      <c r="E12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3">
         <v>6000</v>
       </c>
-      <c r="F12" s="3">
-        <v>4500</v>
-      </c>
-      <c r="G12" s="3">
-        <v>3100</v>
-      </c>
-      <c r="H12" s="3">
-        <v>6100</v>
-      </c>
-      <c r="I12" s="3">
-        <v>6200</v>
+      <c r="G12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J12" s="3">
         <v>6200</v>
       </c>
       <c r="K12" s="3">
+        <v>6200</v>
+      </c>
+      <c r="L12" s="3">
         <v>30800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>32500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>593000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>74900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>35400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>62900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>120700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>45800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>41800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>65600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>17100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>31000</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1142,34 +1159,37 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>1200</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
-        <v>11500</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
         <v>11500</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
+      <c r="K14" s="3">
+        <v>11500</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
@@ -1186,12 +1206,12 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
         <v>3300</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1207,40 +1227,43 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
         <v>100</v>
       </c>
-      <c r="E15" s="3">
-        <v>100</v>
-      </c>
-      <c r="F15" s="3">
-        <v>900</v>
-      </c>
       <c r="G15" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
         <v>100</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1284,8 +1307,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1308,150 +1334,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>5300</v>
-      </c>
-      <c r="E17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="3">
         <v>13400</v>
       </c>
-      <c r="F17" s="3">
-        <v>12400</v>
-      </c>
-      <c r="G17" s="3">
-        <v>15000</v>
-      </c>
-      <c r="H17" s="3">
-        <v>8500</v>
-      </c>
-      <c r="I17" s="3">
-        <v>13300</v>
+      <c r="G17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J17" s="3">
         <v>13300</v>
       </c>
       <c r="K17" s="3">
+        <v>13300</v>
+      </c>
+      <c r="L17" s="3">
         <v>47700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>50300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1044500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>106900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>54600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>87200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>218000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>46900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>132500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>75800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>20500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>33800</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="E18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="3">
         <v>-13400</v>
       </c>
-      <c r="F18" s="3">
-        <v>-12400</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-15000</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-8500</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-13100</v>
+      <c r="G18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J18" s="3">
         <v>-13100</v>
       </c>
       <c r="K18" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="L18" s="3">
         <v>-46300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-48900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1026700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>106300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-54600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-87200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-213700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-44700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-130100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-67500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-17100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-30600</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1477,150 +1510,157 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1600</v>
       </c>
-      <c r="F20" s="3">
-        <v>10500</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1600</v>
-      </c>
-      <c r="I20" s="3">
-        <v>11100</v>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J20" s="3">
         <v>11100</v>
       </c>
       <c r="K20" s="3">
+        <v>11100</v>
+      </c>
+      <c r="L20" s="3">
         <v>9100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>9600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-52900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>41000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>56300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>4500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>5600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>8900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-4800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>7600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>6500</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>-11700</v>
       </c>
-      <c r="F21" s="3">
-        <v>-22100</v>
-      </c>
       <c r="G21" s="3">
-        <v>-8300</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
-        <v>-10000</v>
+        <v>0</v>
       </c>
       <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
         <v>-24100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-24200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-55400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-58500</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>149300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2800</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>-206700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-34900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-134200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-58900</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3">
         <v>-23900</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1645,8 +1685,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1661,108 +1701,114 @@
         <v>0</v>
       </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1400</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="E23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="3">
         <v>-10800</v>
       </c>
-      <c r="F23" s="3">
-        <v>-20500</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-7200</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-9400</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-33400</v>
+      <c r="G23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J23" s="3">
         <v>-33400</v>
       </c>
       <c r="K23" s="3">
+        <v>-33400</v>
+      </c>
+      <c r="L23" s="3">
         <v>-53300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-56300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1079600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>147300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-82900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-208500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-35900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-135300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-61800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-17000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-25500</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1793,15 +1839,15 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3">
         <v>-3100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1700</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
@@ -1815,16 +1861,16 @@
         <v>0</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>200</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
+      <c r="W24" s="3">
+        <v>0</v>
       </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
@@ -1832,8 +1878,11 @@
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1903,150 +1952,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="E26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="3">
         <v>-10800</v>
       </c>
-      <c r="F26" s="3">
-        <v>-20500</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-7200</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-9400</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-33400</v>
+      <c r="G26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J26" s="3">
         <v>-33400</v>
       </c>
       <c r="K26" s="3">
+        <v>-33400</v>
+      </c>
+      <c r="L26" s="3">
         <v>-53300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-56300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1076500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>145600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-82900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-208500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-35900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-135300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-62000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-17200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-25500</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="E27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="3">
         <v>-9100</v>
       </c>
-      <c r="F27" s="3">
-        <v>-20500</v>
-      </c>
-      <c r="G27" s="3">
-        <v>24800</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-16300</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-61800</v>
+      <c r="G27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J27" s="3">
         <v>-61800</v>
       </c>
       <c r="K27" s="3">
+        <v>-61800</v>
+      </c>
+      <c r="L27" s="3">
         <v>-53300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-56300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1076500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>145600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-82900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-213300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-35900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-135300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-62000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-17200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-25500</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2116,8 +2174,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,34 +2186,34 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>1800</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
-        <v>31900</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>-6900</v>
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>-28400</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
         <v>-28400</v>
       </c>
       <c r="K29" s="3">
-        <v>0</v>
+        <v>-28400</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
@@ -2187,8 +2248,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2258,8 +2322,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2329,150 +2396,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>200</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
         <v>1600</v>
       </c>
-      <c r="F32" s="3">
-        <v>-10500</v>
-      </c>
-      <c r="G32" s="3">
-        <v>5900</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-11100</v>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J32" s="3">
         <v>-11100</v>
       </c>
       <c r="K32" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="L32" s="3">
         <v>-9100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-9600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>52900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-41000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-56300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-5600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-8900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>4800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-7600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-6500</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="E33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F33" s="3">
         <v>-9100</v>
       </c>
-      <c r="F33" s="3">
-        <v>-20500</v>
-      </c>
-      <c r="G33" s="3">
-        <v>24800</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-16300</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-61800</v>
+      <c r="G33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J33" s="3">
         <v>-61800</v>
       </c>
       <c r="K33" s="3">
+        <v>-61800</v>
+      </c>
+      <c r="L33" s="3">
         <v>-53300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-56300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1076500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>145600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-82900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-213300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-35900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-135300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-62000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-17200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-25500</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2542,155 +2618,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="E35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" s="3">
         <v>-9100</v>
       </c>
-      <c r="F35" s="3">
-        <v>-20500</v>
-      </c>
-      <c r="G35" s="3">
-        <v>24800</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-16300</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-61800</v>
+      <c r="G35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J35" s="3">
         <v>-61800</v>
       </c>
       <c r="K35" s="3">
+        <v>-61800</v>
+      </c>
+      <c r="L35" s="3">
         <v>-53300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-56300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1076500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>145600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-82900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-213300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-35900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-135300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-62000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-17200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-25500</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43830</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43738</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43646</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43465</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43373</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43281</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2716,8 +2801,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2743,62 +2829,63 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
-        <v>53600</v>
-      </c>
-      <c r="E41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F41" s="3">
         <v>68300</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G41" s="3">
-        <v>152000</v>
+      <c r="G41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I41" s="3">
-        <v>291500</v>
+      <c r="I41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J41" s="3">
         <v>291500</v>
       </c>
       <c r="K41" s="3">
+        <v>291500</v>
+      </c>
+      <c r="L41" s="3">
         <v>325400</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3">
         <v>4342000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>657500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>408700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>221800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>163400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>178800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>200200</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2814,61 +2901,64 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>115000</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>105100</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
-        <v>55500</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>20200</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
         <v>20200</v>
       </c>
       <c r="K42" s="3">
+        <v>20200</v>
+      </c>
+      <c r="L42" s="3">
         <v>80800</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>422300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>3900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>4600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>7700</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
-      </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
+      <c r="T42" s="3">
+        <v>0</v>
       </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
@@ -2885,62 +2975,65 @@
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3">
         <v>1200</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I43" s="3">
-        <v>1800</v>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J43" s="3">
         <v>1800</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
+      <c r="K43" s="3">
+        <v>1800</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3">
         <v>242900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>49400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>10700</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q43" s="3">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3">
         <v>4200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>12300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>18400</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2956,8 +3049,11 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3006,8 +3102,8 @@
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S44" s="3">
-        <v>0</v>
+      <c r="S44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T44" s="3">
         <v>0</v>
@@ -3027,62 +3123,65 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>4600</v>
-      </c>
-      <c r="E45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
         <v>1000</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I45" s="3">
-        <v>16200</v>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J45" s="3">
         <v>16200</v>
       </c>
       <c r="K45" s="3">
+        <v>16200</v>
+      </c>
+      <c r="L45" s="3">
         <v>14100</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>208500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>27000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>19700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>18600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>23300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>17800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>34500</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3098,62 +3197,65 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
-        <v>173200</v>
-      </c>
-      <c r="E46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F46" s="3">
         <v>176700</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G46" s="3">
-        <v>230500</v>
+      <c r="G46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I46" s="3">
-        <v>329900</v>
+      <c r="I46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J46" s="3">
         <v>329900</v>
       </c>
       <c r="K46" s="3">
+        <v>329900</v>
+      </c>
+      <c r="L46" s="3">
         <v>424000</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3">
         <v>5215700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>738300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>443000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>240700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>195500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>216600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>253100</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3169,22 +3271,25 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3">
         <v>30800</v>
       </c>
-      <c r="E47" s="3">
-        <v>30800</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G47" s="3">
-        <v>19000</v>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
@@ -3195,24 +3300,24 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3">
         <v>1600</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3">
         <v>578000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>91900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>105400</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3225,8 +3330,8 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
@@ -3240,62 +3345,65 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>3600</v>
-      </c>
-      <c r="E48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="3">
         <v>3800</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G48" s="3">
-        <v>3900</v>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I48" s="3">
-        <v>5600</v>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J48" s="3">
         <v>5600</v>
       </c>
       <c r="K48" s="3">
+        <v>5600</v>
+      </c>
+      <c r="L48" s="3">
         <v>14100</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3">
         <v>65500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6200</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3311,62 +3419,65 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>0</v>
-      </c>
-      <c r="E49" s="3">
-        <v>0</v>
+      <c r="D49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F49" s="3">
         <v>0</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
+      <c r="G49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
         <v>38800</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>282600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>39100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>39300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>44300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>44700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>45500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>49100</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3382,8 +3493,11 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3453,8 +3567,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3524,59 +3641,62 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>1300</v>
-      </c>
-      <c r="E52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3">
         <v>1400</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G52" s="3">
-        <v>500</v>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I52" s="3">
-        <v>33500</v>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J52" s="3">
         <v>33500</v>
       </c>
       <c r="K52" s="3">
+        <v>33500</v>
+      </c>
+      <c r="L52" s="3">
         <v>5800</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3">
         <v>6100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>300</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
       <c r="P52" s="3">
         <v>0</v>
       </c>
       <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
         <v>2600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>900</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3595,8 +3715,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3666,62 +3789,65 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
-        <v>208900</v>
-      </c>
-      <c r="E54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F54" s="3">
         <v>212700</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G54" s="3">
-        <v>253800</v>
+      <c r="G54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I54" s="3">
-        <v>368900</v>
+      <c r="I54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J54" s="3">
         <v>368900</v>
       </c>
       <c r="K54" s="3">
+        <v>368900</v>
+      </c>
+      <c r="L54" s="3">
         <v>484200</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3">
         <v>6148000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>875100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>593500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>291200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>249600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>268600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>308500</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3737,8 +3863,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3764,8 +3893,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3791,8 +3921,9 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3823,21 +3954,21 @@
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3">
         <v>536200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>77400</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P57" s="3">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3">
         <v>34600</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3853,8 +3984,8 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W57" s="3">
-        <v>0</v>
+      <c r="W57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X57" s="3">
         <v>0</v>
@@ -3862,38 +3993,41 @@
       <c r="Y57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F58" s="3">
         <v>800</v>
       </c>
-      <c r="E58" s="3">
-        <v>800</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>700</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>600</v>
+      <c r="G58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J58" s="3">
         <v>600</v>
       </c>
       <c r="K58" s="3">
+        <v>600</v>
+      </c>
+      <c r="L58" s="3">
         <v>7900</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -3907,17 +4041,17 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>7200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>7300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>7900</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3933,62 +4067,65 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3">
         <v>100</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3">
-        <v>2000</v>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I59" s="3">
-        <v>50900</v>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J59" s="3">
         <v>50900</v>
       </c>
       <c r="K59" s="3">
+        <v>50900</v>
+      </c>
+      <c r="L59" s="3">
         <v>1500</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3">
         <v>14500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>48200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>77300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>61400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>57300</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4004,62 +4141,65 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>7800</v>
-      </c>
-      <c r="E60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F60" s="3">
         <v>8500</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G60" s="3">
-        <v>14000</v>
+      <c r="G60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I60" s="3">
-        <v>58100</v>
+      <c r="I60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J60" s="3">
         <v>58100</v>
       </c>
       <c r="K60" s="3">
+        <v>58100</v>
+      </c>
+      <c r="L60" s="3">
         <v>91400</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3">
         <v>550600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>79600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>48200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>35700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>84500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>68700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>65200</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4075,38 +4215,41 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>3100</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
         <v>3300</v>
       </c>
       <c r="K61" s="3">
+        <v>3300</v>
+      </c>
+      <c r="L61" s="3">
         <v>2800</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -4114,23 +4257,23 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>8900</v>
-      </c>
-      <c r="P61" s="3">
-        <v>9800</v>
       </c>
       <c r="Q61" s="3">
         <v>9800</v>
       </c>
       <c r="R61" s="3">
+        <v>9800</v>
+      </c>
+      <c r="S61" s="3">
         <v>10300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>10600</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4146,8 +4289,11 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4166,42 +4312,42 @@
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I62" s="3">
-        <v>64900</v>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J62" s="3">
         <v>64900</v>
       </c>
       <c r="K62" s="3">
+        <v>64900</v>
+      </c>
+      <c r="L62" s="3">
         <v>15700</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3">
         <v>137700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>18000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>19600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1600</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,8 +4363,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4288,8 +4437,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4359,8 +4511,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4430,62 +4585,65 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
-        <v>10600</v>
-      </c>
-      <c r="E66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F66" s="3">
         <v>11500</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G66" s="3">
-        <v>17200</v>
+      <c r="G66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I66" s="3">
-        <v>126300</v>
+      <c r="I66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J66" s="3">
         <v>126300</v>
       </c>
       <c r="K66" s="3">
+        <v>126300</v>
+      </c>
+      <c r="L66" s="3">
         <v>146800</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3">
         <v>688300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>97600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>76800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>49000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>96000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>80300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>77500</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4501,8 +4659,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4528,8 +4689,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4599,8 +4761,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4670,8 +4835,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4715,17 +4883,17 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>445800</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>425700</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>459900</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
@@ -4741,8 +4909,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4812,62 +4983,65 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>-1289200</v>
-      </c>
-      <c r="E72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3">
         <v>-1286000</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-1256500</v>
+      <c r="G72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I72" s="3">
-        <v>-1263800</v>
+      <c r="I72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J72" s="3">
         <v>-1263800</v>
       </c>
       <c r="K72" s="3">
+        <v>-1263800</v>
+      </c>
+      <c r="L72" s="3">
         <v>-1052800</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3">
         <v>-3099800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-279500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-423200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-437400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-358200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-309300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-295300</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4883,8 +5057,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4954,8 +5131,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5025,8 +5205,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5096,62 +5279,65 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
-        <v>198300</v>
-      </c>
-      <c r="E76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F76" s="3">
         <v>201200</v>
       </c>
-      <c r="F76" s="3">
-        <v>236600</v>
-      </c>
-      <c r="G76" s="3">
-        <v>236600</v>
-      </c>
-      <c r="H76" s="3">
-        <v>242600</v>
-      </c>
-      <c r="I76" s="3">
-        <v>242600</v>
+      <c r="G76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J76" s="3">
         <v>242600</v>
       </c>
       <c r="K76" s="3">
+        <v>242600</v>
+      </c>
+      <c r="L76" s="3">
         <v>337400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>437900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5459700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>777400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>516600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>242200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-292200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-237300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-228900</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5167,8 +5353,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5238,155 +5427,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43830</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43738</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43646</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43465</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43373</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43281</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="E81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F81" s="3">
         <v>-9100</v>
       </c>
-      <c r="F81" s="3">
-        <v>-20500</v>
-      </c>
-      <c r="G81" s="3">
-        <v>24800</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-16300</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-61800</v>
+      <c r="G81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J81" s="3">
         <v>-61800</v>
       </c>
       <c r="K81" s="3">
+        <v>-61800</v>
+      </c>
+      <c r="L81" s="3">
         <v>-53300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-56300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1076500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>145600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-82900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-213300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-35900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-135300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-62000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-17200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-25500</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5412,8 +5610,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5438,39 +5637,39 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3">
         <v>2500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2600</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3">
         <v>2000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1100</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3">
         <v>1400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1000</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5483,8 +5682,11 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5554,8 +5756,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5625,8 +5830,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5696,8 +5904,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5767,8 +5978,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5838,8 +6052,11 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5873,30 +6090,30 @@
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3">
         <v>59900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-80400</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3">
         <v>-124700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-95200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-61400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-43200</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5909,8 +6126,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5936,8 +6156,9 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5968,8 +6189,8 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -5981,20 +6202,20 @@
         <v>0</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-1800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2200</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6007,8 +6228,11 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6078,8 +6302,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6149,8 +6376,11 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6184,30 +6414,30 @@
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3">
         <v>-27900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-35400</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3">
         <v>30500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>19700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>24900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>1500</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6220,8 +6450,11 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6247,8 +6480,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6279,8 +6513,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6318,8 +6552,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6389,8 +6626,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6460,8 +6700,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6531,8 +6774,11 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6566,30 +6812,30 @@
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3">
         <v>475300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>358400</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3">
         <v>21900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>5800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-4700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>227800</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6602,8 +6848,11 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6628,39 +6877,39 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
         <v>16700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>17600</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3">
         <v>-14700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1400</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3">
         <v>2200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>11300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>9200</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6673,8 +6922,11 @@
       <c r="Y101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6705,33 +6957,33 @@
       <c r="L102" s="3">
         <v>0</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3">
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3">
         <v>492600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>244000</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3">
         <v>-70000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-58400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-41700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>195300</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6742,6 +6994,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
